--- a/data/Hasbro Black Series Catalog.xlsx
+++ b/data/Hasbro Black Series Catalog.xlsx
@@ -534,7 +534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/orange-wave-2013/luke-skywalker-x-wing-pilot-1.php</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-x-wing-pilot-1.jpg</v>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -584,7 +584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/orange-wave-2013/darth-maul-2.php</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-maul-2.jpg</v>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -634,7 +634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/orange-wave-2013/sandtrooper-3.php</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sandtrooper-3.jpg</v>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -684,7 +684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/orange-wave-2013/r2-d2-4.php</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/r2-d2-4.jpg</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -734,7 +734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/orange-wave-2013/princess-leia-slave-outfit-5.php</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/princess-leia-slave-outfit-5.jpg</v>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -784,7 +784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/orange-wave-2013/boba-fett-6.php</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-6.jpg</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -834,7 +834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/orange-wave-2013/greedo-7.php</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/greedo-7.jpg</v>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -884,7 +884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/orange-wave-2013/han-solo-anh-8.php</v>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-anh-8.jpg</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -934,7 +934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/orange-wave-2013/stormtrooper-9.php</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/stormtrooper-9.jpg</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -984,7 +984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/orange-wave-2013/obi-wan-kenobi-orange-line-10.php</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-orange-line-10.jpg</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -1034,7 +1034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/orange-wave-2013/luke-skywalker-bespin-11.php</v>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-bespin-11.jpg</v>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -1084,7 +1084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/orange-wave-2013/anakin-skywalker-12.php</v>
       </c>
       <c r="L13" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/anakin-skywalker-12.jpg</v>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -1134,7 +1134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/orange-wave-2013/clone-trooper-13.php</v>
       </c>
       <c r="L14" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-trooper-13.jpg</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -1184,7 +1184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/blue-wave-2014-2015/sandtrooper-corporal-14.php</v>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sandtrooper-corporal-14.jpg</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1234,7 +1234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/blue-wave-2014-2015/darth-vader-15.php</v>
       </c>
       <c r="L16" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-15.jpg</v>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -1284,7 +1284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/blue-wave-2014-2015/luke-skywalker-jedi-knight-16.php</v>
       </c>
       <c r="L17" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-jedi-knight-16.jpg</v>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1334,7 +1334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/blue-wave-2014-2015/chewbacca-blue-line-17.php</v>
       </c>
       <c r="L18" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/chewbacca-blue-line-17.jpg</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1384,7 +1384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/blue-wave-2014-2015/tie-pilot-19.php</v>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/tie-pilot-19.jpg</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1434,7 +1434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/blue-wave-2014-2015/yoda-18.php</v>
       </c>
       <c r="L20" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/yoda-18.jpg</v>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -1484,7 +1484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/blue-wave-2014-2015/clone-trooper-sergeant-20.php</v>
       </c>
       <c r="L21" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-trooper-sergeant-20.jpg</v>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -1534,7 +1534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/blue-wave-2014-2015/obi-wan-kenobi-blue-line-21.php</v>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-blue-line-21.jpg</v>
       </c>
       <c r="M22" t="str">
         <v/>
@@ -1584,7 +1584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/blue-wave-2014-2015/han-solo-stormtrooper-disguise-22.php</v>
       </c>
       <c r="L23" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-stormtrooper-disguise-22.jpg</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -1634,7 +1634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/blue-wave-2014-2015/bossk-23.php</v>
       </c>
       <c r="L24" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/bossk-23.jpg</v>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -1684,7 +1684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/blue-wave-2014-2015/emperor-palpatine-24.php</v>
       </c>
       <c r="L25" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/emperor-palpatine-24.jpg</v>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -1734,7 +1734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/blue-wave-2014-2015/luke-skywalker-stormtrooper-disguise-25.php</v>
       </c>
       <c r="L26" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-stormtrooper-disguise-25.jpg</v>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -1784,7 +1784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/blue-wave-2014-2015/clone-trooper-captain-26.php</v>
       </c>
       <c r="L27" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-trooper-captain-26.jpg</v>
       </c>
       <c r="M27" t="str">
         <v/>
@@ -1834,7 +1834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/blue-wave-2014-2015/clone-commander-cody-27.php</v>
       </c>
       <c r="L28" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-commander-cody-27.jpg</v>
       </c>
       <c r="M28" t="str">
         <v/>
@@ -1884,7 +1884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/blue-wave-2014-2015/ig-88-28.php</v>
       </c>
       <c r="L29" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ig-88-28.jpg</v>
       </c>
       <c r="M29" t="str">
         <v/>
@@ -1934,7 +1934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/blue-wave-2014-2015/princess-leia-organa-boushh-29.php</v>
       </c>
       <c r="L30" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/princess-leia-organa-boushh-29.jpg</v>
       </c>
       <c r="M30" t="str">
         <v/>
@@ -1984,7 +1984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/finn-jakku-30.php</v>
       </c>
       <c r="L31" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/finn-jakku-30.jpg</v>
       </c>
       <c r="M31" t="str">
         <v/>
@@ -2034,7 +2034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/rey-and-bb-8-31.php</v>
       </c>
       <c r="L32" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rey-and-bb-8-31.jpg</v>
       </c>
       <c r="M32" t="str">
         <v/>
@@ -2084,7 +2084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/kylo-ren-32.php</v>
       </c>
       <c r="L33" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kylo-ren-32.jpg</v>
       </c>
       <c r="M33" t="str">
         <v/>
@@ -2134,7 +2134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/first-order-stormtrooper-33.php</v>
       </c>
       <c r="L34" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/first-order-stormtrooper-33.jpg</v>
       </c>
       <c r="M34" t="str">
         <v/>
@@ -2184,7 +2184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/chewbacca-34.php</v>
       </c>
       <c r="L35" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/chewbacca-34.jpg</v>
       </c>
       <c r="M35" t="str">
         <v/>
@@ -2234,7 +2234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/captain-phasma-35.php</v>
       </c>
       <c r="L36" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/captain-phasma-35.jpg</v>
       </c>
       <c r="M36" t="str">
         <v/>
@@ -2284,7 +2284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/poe-dameron-36.php</v>
       </c>
       <c r="L37" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/poe-dameron-36.jpg</v>
       </c>
       <c r="M37" t="str">
         <v/>
@@ -2334,7 +2334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/guavian-enforcer-37.php</v>
       </c>
       <c r="L38" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/guavian-enforcer-37.jpg</v>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -2384,7 +2384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/constable-zuvio-38.php</v>
       </c>
       <c r="L39" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/constable-zuvio-38.jpg</v>
       </c>
       <c r="M39" t="str">
         <v/>
@@ -2434,7 +2434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/resistance-trooper-39.php</v>
       </c>
       <c r="L40" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/resistance-trooper-39.jpg</v>
       </c>
       <c r="M40" t="str">
         <v/>
@@ -2484,7 +2484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/first-order-tie-pilot-40.php</v>
       </c>
       <c r="L41" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/first-order-tie-pilot-40.jpg</v>
       </c>
       <c r="M41" t="str">
         <v/>
@@ -2534,7 +2534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/first-order-snowtrooper-41.php</v>
       </c>
       <c r="L42" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/first-order-snowtrooper-41.jpg</v>
       </c>
       <c r="M42" t="str">
         <v/>
@@ -2584,7 +2584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/general-hux-42.php</v>
       </c>
       <c r="L43" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/general-hux-42.jpg</v>
       </c>
       <c r="M43" t="str">
         <v/>
@@ -2634,7 +2634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/x-wing-pilot-asty-43.php</v>
       </c>
       <c r="L44" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/x-wing-pilot-asty-43.jpg</v>
       </c>
       <c r="M44" t="str">
         <v/>
@@ -2684,7 +2684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/jango-fett-44.php</v>
       </c>
       <c r="L45" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jango-fett-44.jpg</v>
       </c>
       <c r="M45" t="str">
         <v/>
@@ -2734,7 +2734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/first-order-flametrooper-45.php</v>
       </c>
       <c r="L46" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/first-order-flametrooper-45.jpg</v>
       </c>
       <c r="M46" t="str">
         <v/>
@@ -2784,7 +2784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/finn-fn-2187-46.php</v>
       </c>
       <c r="L47" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/finn-fn-2187-46.jpg</v>
       </c>
       <c r="M47" t="str">
         <v/>
@@ -2834,7 +2834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/han-solo-tfa-47.php</v>
       </c>
       <c r="L48" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-tfa-47.jpg</v>
       </c>
       <c r="M48" t="str">
         <v/>
@@ -2884,7 +2884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/kanan-jarrus-48.php</v>
       </c>
       <c r="L49" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kanan-jarrus-48.jpg</v>
       </c>
       <c r="M49" t="str">
         <v/>
@@ -2934,7 +2934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/ahsoka-tano-49.php</v>
       </c>
       <c r="L50" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ahsoka-tano-49.jpg</v>
       </c>
       <c r="M50" t="str">
         <v/>
@@ -2984,7 +2984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/luke-skywalker-anh-50.php</v>
       </c>
       <c r="L51" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-anh-50.jpg</v>
       </c>
       <c r="M51" t="str">
         <v/>
@@ -3034,7 +3034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/sergeant-jyn-erso-146.php</v>
       </c>
       <c r="L52" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sergeant-jyn-erso-146.jpg</v>
       </c>
       <c r="M52" t="str">
         <v/>
@@ -3084,7 +3084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/captain-cassian-andor-eadu-147.php</v>
       </c>
       <c r="L53" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/captain-cassian-andor-eadu-147.jpg</v>
       </c>
       <c r="M53" t="str">
         <v/>
@@ -3134,7 +3134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/k-2so-imperial-security-droid-148.php</v>
       </c>
       <c r="L54" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/k-2so-imperial-security-droid-148.jpg</v>
       </c>
       <c r="M54" t="str">
         <v/>
@@ -3184,7 +3184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/imperial-death-trooper-149.php</v>
       </c>
       <c r="L55" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-death-trooper-149.jpg</v>
       </c>
       <c r="M55" t="str">
         <v/>
@@ -3234,7 +3234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/kylo-ren-unmasked-150.php</v>
       </c>
       <c r="L56" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kylo-ren-unmasked-150.jpg</v>
       </c>
       <c r="M56" t="str">
         <v/>
@@ -3284,7 +3284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/director-krennic-175.php</v>
       </c>
       <c r="L57" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/director-krennic-175.jpg</v>
       </c>
       <c r="M57" t="str">
         <v/>
@@ -3334,7 +3334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/scarif-stormtrooper-squad-leader-176.php</v>
       </c>
       <c r="L58" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/scarif-stormtrooper-squad-leader-176.jpg</v>
       </c>
       <c r="M58" t="str">
         <v/>
@@ -3384,7 +3384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/c-3po-red-arm-177.php</v>
       </c>
       <c r="L59" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/c-3po-red-arm-177.jpg</v>
       </c>
       <c r="M59" t="str">
         <v/>
@@ -3434,7 +3434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/princess-leia-organa-178.php</v>
       </c>
       <c r="L60" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/princess-leia-organa-178.jpg</v>
       </c>
       <c r="M60" t="str">
         <v/>
@@ -3484,7 +3484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/at-at-driver-179.php</v>
       </c>
       <c r="L61" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/at-at-driver-179.jpg</v>
       </c>
       <c r="M61" t="str">
         <v/>
@@ -3534,7 +3534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/obi-wan-kenobi-anh-180.php</v>
       </c>
       <c r="L62" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-anh-180.jpg</v>
       </c>
       <c r="M62" t="str">
         <v/>
@@ -3584,7 +3584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/sabine-wren-33-181.php</v>
       </c>
       <c r="L63" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sabine-wren-33-181.jpg</v>
       </c>
       <c r="M63" t="str">
         <v/>
@@ -3634,7 +3634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/darth-revan-182.php</v>
       </c>
       <c r="L64" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-revan-182.jpg</v>
       </c>
       <c r="M64" t="str">
         <v/>
@@ -3684,7 +3684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/snowtrooper-esb-183.php</v>
       </c>
       <c r="L65" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/snowtrooper-esb-183.jpg</v>
       </c>
       <c r="M65" t="str">
         <v/>
@@ -3734,7 +3734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/chirrut-imwe-36-197.php</v>
       </c>
       <c r="L66" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/chirrut-imwe-36-197.jpg</v>
       </c>
       <c r="M66" t="str">
         <v/>
@@ -3784,7 +3784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/baze-malbus-198.php</v>
       </c>
       <c r="L67" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/baze-malbus-198.jpg</v>
       </c>
       <c r="M67" t="str">
         <v/>
@@ -3834,7 +3834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/emperors-royal-guard-259.php</v>
       </c>
       <c r="L68" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/emperors-royal-guard-259.jpg</v>
       </c>
       <c r="M68" t="str">
         <v/>
@@ -3884,7 +3884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/lando-calrissian-258.php</v>
       </c>
       <c r="L69" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/lando-calrissian-258.jpg</v>
       </c>
       <c r="M69" t="str">
         <v/>
@@ -3934,7 +3934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/qui-gon-jinn-261.php</v>
       </c>
       <c r="L70" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/qui-gon-jinn-261.jpg</v>
       </c>
       <c r="M70" t="str">
         <v/>
@@ -3984,7 +3984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/tusken-raider-260.php</v>
       </c>
       <c r="L71" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/tusken-raider-260.jpg</v>
       </c>
       <c r="M71" t="str">
         <v/>
@@ -4034,7 +4034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/hera-syndulla-42-262.php</v>
       </c>
       <c r="L72" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/hera-syndulla-42-262.jpg</v>
       </c>
       <c r="M72" t="str">
         <v/>
@@ -4084,7 +4084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/darth-vader-anh-257.php</v>
       </c>
       <c r="L73" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-anh-257.jpg</v>
       </c>
       <c r="M73" t="str">
         <v/>
@@ -4134,7 +4134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/rey-jedi-training-578.php</v>
       </c>
       <c r="L74" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rey-jedi-training-578.jpg</v>
       </c>
       <c r="M74" t="str">
         <v/>
@@ -4184,7 +4184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/kylo-ren-last-jedi-580.php</v>
       </c>
       <c r="L75" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kylo-ren-last-jedi-580.jpg</v>
       </c>
       <c r="M75" t="str">
         <v/>
@@ -4234,7 +4234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/luke-jedi-master-581.php</v>
       </c>
       <c r="L76" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-jedi-master-581.jpg</v>
       </c>
       <c r="M76" t="str">
         <v/>
@@ -4284,7 +4284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/grand-admiral-thrawn-641.php</v>
       </c>
       <c r="L77" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/grand-admiral-thrawn-641.jpg</v>
       </c>
       <c r="M77" t="str">
         <v/>
@@ -4334,7 +4334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/stormtrooper-repack-642.php</v>
       </c>
       <c r="L78" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/stormtrooper-repack-642.jpg</v>
       </c>
       <c r="M78" t="str">
         <v/>
@@ -4384,7 +4384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/maz-kanata-356.php</v>
       </c>
       <c r="L79" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/maz-kanata-356.jpg</v>
       </c>
       <c r="M79" t="str">
         <v/>
@@ -4434,7 +4434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/elite-praetorian-guard-657.php</v>
       </c>
       <c r="L80" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/elite-praetorian-guard-657.jpg</v>
       </c>
       <c r="M80" t="str">
         <v/>
@@ -4484,7 +4484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/finn-first-order-disguise-579.php</v>
       </c>
       <c r="L81" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/finn-first-order-disguise-579.jpg</v>
       </c>
       <c r="M81" t="str">
         <v/>
@@ -4534,7 +4534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/general-leia-358.php</v>
       </c>
       <c r="L82" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/general-leia-358.jpg</v>
       </c>
       <c r="M82" t="str">
         <v/>
@@ -4584,7 +4584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/captain-poe-dameron-656.php</v>
       </c>
       <c r="L83" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/captain-poe-dameron-656.jpg</v>
       </c>
       <c r="M83" t="str">
         <v/>
@@ -4634,7 +4634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/snoke-677.php</v>
       </c>
       <c r="L84" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/snoke-677.jpg</v>
       </c>
       <c r="M84" t="str">
         <v/>
@@ -4684,7 +4684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/rose-684.php</v>
       </c>
       <c r="L85" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rose-684.jpg</v>
       </c>
       <c r="M85" t="str">
         <v/>
@@ -4734,7 +4734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/jaina-solo-344.php</v>
       </c>
       <c r="L86" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jaina-solo-344.jpg</v>
       </c>
       <c r="M86" t="str">
         <v/>
@@ -4784,7 +4784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/dj-canto-bight-the-last-jedi-792.php</v>
       </c>
       <c r="L87" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/dj-canto-bight-the-last-jedi-792.jpg</v>
       </c>
       <c r="M87" t="str">
         <v/>
@@ -4834,7 +4834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/rey-island-journey-794.php</v>
       </c>
       <c r="L88" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rey-island-journey-794.jpg</v>
       </c>
       <c r="M88" t="str">
         <v/>
@@ -4884,7 +4884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/clone-captain-rex-934.php</v>
       </c>
       <c r="L89" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-captain-rex-934.jpg</v>
       </c>
       <c r="M89" t="str">
         <v/>
@@ -4934,7 +4934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/death-star-trooper-1025.php</v>
       </c>
       <c r="L90" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/death-star-trooper-1025.jpg</v>
       </c>
       <c r="M90" t="str">
         <v/>
@@ -4984,7 +4984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/jawa-1024.php</v>
       </c>
       <c r="L91" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jawa-1024.jpg</v>
       </c>
       <c r="M91" t="str">
         <v/>
@@ -5034,7 +5034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/han-solo-solo-1012.php</v>
       </c>
       <c r="L92" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-solo-1012.jpg</v>
       </c>
       <c r="M92" t="str">
         <v/>
@@ -5084,7 +5084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/grand-moff-tarkin-345.php</v>
       </c>
       <c r="L93" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/grand-moff-tarkin-345.jpg</v>
       </c>
       <c r="M93" t="str">
         <v/>
@@ -5134,7 +5134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/range-trooper-1022.php</v>
       </c>
       <c r="L94" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/range-trooper-1022.jpg</v>
       </c>
       <c r="M94" t="str">
         <v/>
@@ -5184,7 +5184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/lando-1015.php</v>
       </c>
       <c r="L95" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/lando-1015.jpg</v>
       </c>
       <c r="M95" t="str">
         <v/>
@@ -5234,7 +5234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/qi-ra-1014.php</v>
       </c>
       <c r="L96" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/qi-ra-1014.jpg</v>
       </c>
       <c r="M96" t="str">
         <v/>
@@ -5284,7 +5284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/4-lom-790.php</v>
       </c>
       <c r="L97" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/4-lom-790.jpg</v>
       </c>
       <c r="M97" t="str">
         <v/>
@@ -5334,7 +5334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/tobias-beckett-1013.php</v>
       </c>
       <c r="L98" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/tobias-beckett-1013.jpg</v>
       </c>
       <c r="M98" t="str">
         <v/>
@@ -5384,7 +5384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/rebel-fleet-trooper-354.php</v>
       </c>
       <c r="L99" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rebel-fleet-trooper-354.jpg</v>
       </c>
       <c r="M99" t="str">
         <v/>
@@ -5434,7 +5434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/han-solo-bespin-1045.php</v>
       </c>
       <c r="L100" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-bespin-1045.jpg</v>
       </c>
       <c r="M100" t="str">
         <v/>
@@ -5484,7 +5484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/val-vandor-1-1046.php</v>
       </c>
       <c r="L101" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/val-vandor-1-1046.jpg</v>
       </c>
       <c r="M101" t="str">
         <v/>
@@ -5534,7 +5534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/imperial-patrol-trooper-1047.php</v>
       </c>
       <c r="L102" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-patrol-trooper-1047.jpg</v>
       </c>
       <c r="M102" t="str">
         <v/>
@@ -5584,7 +5584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/l3-37-1048.php</v>
       </c>
       <c r="L103" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/l3-37-1048.jpg</v>
       </c>
       <c r="M103" t="str">
         <v/>
@@ -5634,7 +5634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/dengar-791.php</v>
       </c>
       <c r="L104" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/dengar-791.jpg</v>
       </c>
       <c r="M104" t="str">
         <v/>
@@ -5684,7 +5684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/princess-leia-organa-hoth-1011.php</v>
       </c>
       <c r="L105" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/princess-leia-organa-hoth-1011.jpg</v>
       </c>
       <c r="M105" t="str">
         <v/>
@@ -5734,7 +5734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/lando-calrissian-skiff-guard-disguise-793.php</v>
       </c>
       <c r="L106" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/lando-calrissian-skiff-guard-disguise-793.jpg</v>
       </c>
       <c r="M106" t="str">
         <v/>
@@ -5784,7 +5784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/rio-durant-1093.php</v>
       </c>
       <c r="L107" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rio-durant-1093.jpg</v>
       </c>
       <c r="M107" t="str">
         <v/>
@@ -5834,7 +5834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/han-solo-mimban-1221.php</v>
       </c>
       <c r="L108" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-mimban-1221.jpg</v>
       </c>
       <c r="M108" t="str">
         <v/>
@@ -5884,7 +5884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/dryden-vos-1125.php</v>
       </c>
       <c r="L109" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/dryden-vos-1125.jpg</v>
       </c>
       <c r="M109" t="str">
         <v/>
@@ -5934,7 +5934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/vice-admiral-holdo-1016.php</v>
       </c>
       <c r="L110" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/vice-admiral-holdo-1016.jpg</v>
       </c>
       <c r="M110" t="str">
         <v/>
@@ -5984,7 +5984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/padme-amidala-1220.php</v>
       </c>
       <c r="L111" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/padme-amidala-1220.jpg</v>
       </c>
       <c r="M111" t="str">
         <v/>
@@ -6034,7 +6034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/mace-windu-1218.php</v>
       </c>
       <c r="L112" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mace-windu-1218.jpg</v>
       </c>
       <c r="M112" t="str">
         <v/>
@@ -6084,7 +6084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/battle-droid-1219.php</v>
       </c>
       <c r="L113" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/battle-droid-1219.jpg</v>
       </c>
       <c r="M113" t="str">
         <v/>
@@ -6134,7 +6134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/chopper-84-1246.php</v>
       </c>
       <c r="L114" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/chopper-84-1246.jpg</v>
       </c>
       <c r="M114" t="str">
         <v/>
@@ -6184,7 +6184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/obi-wan-kenobi-padawan-1242.php</v>
       </c>
       <c r="L115" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-padawan-1242.jpg</v>
       </c>
       <c r="M115" t="str">
         <v/>
@@ -6234,7 +6234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/ezra-bridger-86-1245.php</v>
       </c>
       <c r="L116" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ezra-bridger-86-1245.jpg</v>
       </c>
       <c r="M116" t="str">
         <v/>
@@ -6284,7 +6284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/doctor-aphra-1243.php</v>
       </c>
       <c r="L117" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/doctor-aphra-1243.jpg</v>
       </c>
       <c r="M117" t="str">
         <v/>
@@ -6334,7 +6334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/bt-1-1244.php</v>
       </c>
       <c r="L118" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/bt-1-1244.jpg</v>
       </c>
       <c r="M118" t="str">
         <v/>
@@ -6384,7 +6384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/0-0-0-triple-zero-1241.php</v>
       </c>
       <c r="L119" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/0-0-0-triple-zero-1241.jpg</v>
       </c>
       <c r="M119" t="str">
         <v/>
@@ -6434,7 +6434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/supreme-leader-kylo-ren-1287.php</v>
       </c>
       <c r="L120" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/supreme-leader-kylo-ren-1287.jpg</v>
       </c>
       <c r="M120" t="str">
         <v/>
@@ -6484,7 +6484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/supreme-leader-kylo-ren-first-edition-1864.php</v>
       </c>
       <c r="L121" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/supreme-leader-kylo-ren-first-edition-1864.jpg</v>
       </c>
       <c r="M121" t="str">
         <v/>
@@ -6534,7 +6534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/rey-d-o-first-edition-1865.php</v>
       </c>
       <c r="L122" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rey-d-o-first-edition-1865.jpg</v>
       </c>
       <c r="M122" t="str">
         <v/>
@@ -6584,7 +6584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/rey-d-o-1288.php</v>
       </c>
       <c r="L123" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rey-d-o-1288.jpg</v>
       </c>
       <c r="M123" t="str">
         <v/>
@@ -6634,7 +6634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/sith-trooper-first-edition-1866.php</v>
       </c>
       <c r="L124" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sith-trooper-first-edition-1866.jpg</v>
       </c>
       <c r="M124" t="str">
         <v/>
@@ -6684,7 +6684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/sith-trooper-1289.php</v>
       </c>
       <c r="L125" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sith-trooper-1289.jpg</v>
       </c>
       <c r="M125" t="str">
         <v/>
@@ -6734,7 +6734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/cal-kestis-first-edition-1867.php</v>
       </c>
       <c r="L126" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cal-kestis-first-edition-1867.jpg</v>
       </c>
       <c r="M126" t="str">
         <v/>
@@ -6784,7 +6784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/cal-kestis-1290.php</v>
       </c>
       <c r="L127" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cal-kestis-1290.jpg</v>
       </c>
       <c r="M127" t="str">
         <v/>
@@ -6834,7 +6834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/the-mandalorian-1291.php</v>
       </c>
       <c r="L128" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-mandalorian-1291.jpg</v>
       </c>
       <c r="M128" t="str">
         <v/>
@@ -6884,7 +6884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/the-mandalorian-first-edition-1400.php</v>
       </c>
       <c r="L129" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-mandalorian-first-edition-1400.jpg</v>
       </c>
       <c r="M129" t="str">
         <v/>
@@ -6934,7 +6934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/second-sister-inquisitor-first-edition-1868.php</v>
       </c>
       <c r="L130" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/second-sister-inquisitor-first-edition-1868.jpg</v>
       </c>
       <c r="M130" t="str">
         <v/>
@@ -6984,7 +6984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/second-sister-inquisitor-1292.php</v>
       </c>
       <c r="L131" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/second-sister-inquisitor-1292.jpg</v>
       </c>
       <c r="M131" t="str">
         <v/>
@@ -7034,7 +7034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/offworld-jawa-1294.php</v>
       </c>
       <c r="L132" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/offworld-jawa-1294.jpg</v>
       </c>
       <c r="M132" t="str">
         <v/>
@@ -7084,7 +7084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/offworld-jawa-first-edition-1869.php</v>
       </c>
       <c r="L133" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/offworld-jawa-first-edition-1869.jpg</v>
       </c>
       <c r="M133" t="str">
         <v/>
@@ -7134,7 +7134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/first-order-stormtrooper-first-edition-1870.php</v>
       </c>
       <c r="L134" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/first-order-stormtrooper-first-edition-1870.jpg</v>
       </c>
       <c r="M134" t="str">
         <v/>
@@ -7184,7 +7184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/first-order-stormtrooper-riot-baton-1295.php</v>
       </c>
       <c r="L135" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/first-order-stormtrooper-riot-baton-1295.jpg</v>
       </c>
       <c r="M135" t="str">
         <v/>
@@ -7234,7 +7234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/jannah-1313.php</v>
       </c>
       <c r="L136" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jannah-1313.jpg</v>
       </c>
       <c r="M136" t="str">
         <v/>
@@ -7284,7 +7284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/first-order-jet-trooper-1318.php</v>
       </c>
       <c r="L137" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/first-order-jet-trooper-1318.jpg</v>
       </c>
       <c r="M137" t="str">
         <v/>
@@ -7334,7 +7334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/luke-skywalker-yavin-ceremony-1296.php</v>
       </c>
       <c r="L138" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-yavin-ceremony-1296.jpg</v>
       </c>
       <c r="M138" t="str">
         <v/>
@@ -7384,7 +7384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/cara-dune-1312.php</v>
       </c>
       <c r="L139" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cara-dune-1312.jpg</v>
       </c>
       <c r="M139" t="str">
         <v/>
@@ -7434,7 +7434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/wedge-antilles-1297.php</v>
       </c>
       <c r="L140" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/wedge-antilles-1297.jpg</v>
       </c>
       <c r="M140" t="str">
         <v/>
@@ -7484,7 +7484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/zorii-bliss-1341.php</v>
       </c>
       <c r="L141" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/zorii-bliss-1341.jpg</v>
       </c>
       <c r="M141" t="str">
         <v/>
@@ -7534,7 +7534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/clone-commander-bly-1401.php</v>
       </c>
       <c r="L142" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-commander-bly-1401.jpg</v>
       </c>
       <c r="M142" t="str">
         <v/>
@@ -7584,7 +7584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/knight-of-ren-1342.php</v>
       </c>
       <c r="L143" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/knight-of-ren-1342.jpg</v>
       </c>
       <c r="M143" t="str">
         <v/>
@@ -7634,7 +7634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/sith-jet-trooper-1402.php</v>
       </c>
       <c r="L144" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sith-jet-trooper-1402.jpg</v>
       </c>
       <c r="M144" t="str">
         <v/>
@@ -7684,7 +7684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/count-dooku-1403.php</v>
       </c>
       <c r="L145" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/count-dooku-1403.jpg</v>
       </c>
       <c r="M145" t="str">
         <v/>
@@ -7734,7 +7734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/geonosis-battle-droid-1404.php</v>
       </c>
       <c r="L146" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/geonosis-battle-droid-1404.jpg</v>
       </c>
       <c r="M146" t="str">
         <v/>
@@ -7784,7 +7784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/plo-koon-1405.php</v>
       </c>
       <c r="L147" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/plo-koon-1405.jpg</v>
       </c>
       <c r="M147" t="str">
         <v/>
@@ -7834,7 +7834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/anakin-skywalker-padawan-1343.php</v>
       </c>
       <c r="L148" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/anakin-skywalker-padawan-1343.jpg</v>
       </c>
       <c r="M148" t="str">
         <v/>
@@ -7884,7 +7884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/obi-wan-kenobi-jedi-knight-1344.php</v>
       </c>
       <c r="L149" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-jedi-knight-1344.jpg</v>
       </c>
       <c r="M149" t="str">
         <v/>
@@ -7934,7 +7934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/force-awakens-2015-2018/kit-fisto-1406.php</v>
       </c>
       <c r="L150" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kit-fisto-1406.jpg</v>
       </c>
       <c r="M150" t="str">
         <v/>
@@ -7984,7 +7984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/the-mandalorian-ahsoka-tano-grogu-3-pack-5227.php</v>
       </c>
       <c r="L151" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-mandalorian-ahsoka-tano-grogu-3-pack-5227.jpg</v>
       </c>
       <c r="M151" t="str">
         <v/>
@@ -8034,7 +8034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/clone-commando-urban-fighter-b1-battle-droid-training-9044.php</v>
       </c>
       <c r="L152" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-commando-urban-fighter-b1-battle-droid-training-9044.jpg</v>
       </c>
       <c r="M152" t="str">
         <v/>
@@ -8084,7 +8084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/dagan-gera-bx-droid-hybrid-9043.php</v>
       </c>
       <c r="L153" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/dagan-gera-bx-droid-hybrid-9043.jpg</v>
       </c>
       <c r="M153" t="str">
         <v/>
@@ -8134,7 +8134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/purge-trooper-patrol-trooper-12165.php</v>
       </c>
       <c r="L154" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/purge-trooper-patrol-trooper-12165.jpg</v>
       </c>
       <c r="M154" t="str">
         <v/>
@@ -8184,7 +8184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/ahsoka-tano-ahsoka-7128.php</v>
       </c>
       <c r="L155" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ahsoka-tano-ahsoka-7128.jpg</v>
       </c>
       <c r="M155" t="str">
         <v/>
@@ -8234,7 +8234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/ezra-bridger-lothal-7205.php</v>
       </c>
       <c r="L156" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ezra-bridger-lothal-7205.jpg</v>
       </c>
       <c r="M156" t="str">
         <v/>
@@ -8284,7 +8284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/sabine-wren-ahsoka-7129.php</v>
       </c>
       <c r="L157" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sabine-wren-ahsoka-7129.jpg</v>
       </c>
       <c r="M157" t="str">
         <v/>
@@ -8334,7 +8334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/morgan-elsbeth-7206.php</v>
       </c>
       <c r="L158" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/morgan-elsbeth-7206.jpg</v>
       </c>
       <c r="M158" t="str">
         <v/>
@@ -8384,7 +8384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/hk-87-assassin-droid-7207.php</v>
       </c>
       <c r="L159" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/hk-87-assassin-droid-7207.jpg</v>
       </c>
       <c r="M159" t="str">
         <v/>
@@ -8434,7 +8434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/hera-syndulla-ahsoka-7130.php</v>
       </c>
       <c r="L160" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/hera-syndulla-ahsoka-7130.jpg</v>
       </c>
       <c r="M160" t="str">
         <v/>
@@ -8484,7 +8484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/professor-huyang-7204.php</v>
       </c>
       <c r="L161" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/professor-huyang-7204.jpg</v>
       </c>
       <c r="M161" t="str">
         <v/>
@@ -8534,7 +8534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/marrok-7208.php</v>
       </c>
       <c r="L162" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/marrok-7208.jpg</v>
       </c>
       <c r="M162" t="str">
         <v/>
@@ -8584,7 +8584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/baylan-skoll-7241.php</v>
       </c>
       <c r="L163" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/baylan-skoll-7241.jpg</v>
       </c>
       <c r="M163" t="str">
         <v/>
@@ -8634,7 +8634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/shin-hati-7242.php</v>
       </c>
       <c r="L164" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/shin-hati-7242.jpg</v>
       </c>
       <c r="M164" t="str">
         <v/>
@@ -8684,7 +8684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/ahsoka-tano-peridea-8781.php</v>
       </c>
       <c r="L165" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ahsoka-tano-peridea-8781.jpg</v>
       </c>
       <c r="M165" t="str">
         <v/>
@@ -8734,7 +8734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/grand-admiral-thrawn-ahsoka-7927.php</v>
       </c>
       <c r="L166" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/grand-admiral-thrawn-ahsoka-7927.jpg</v>
       </c>
       <c r="M166" t="str">
         <v/>
@@ -8784,7 +8784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/baylan-skoll-mercenary-8349.php</v>
       </c>
       <c r="L167" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/baylan-skoll-mercenary-8349.jpg</v>
       </c>
       <c r="M167" t="str">
         <v/>
@@ -8834,7 +8834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/shin-hati-arcana-8692.php</v>
       </c>
       <c r="L168" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/shin-hati-arcana-8692.jpg</v>
       </c>
       <c r="M168" t="str">
         <v/>
@@ -8884,7 +8884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/clone-captain-rex-ahsoka-9438.php</v>
       </c>
       <c r="L169" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-captain-rex-ahsoka-9438.jpg</v>
       </c>
       <c r="M169" t="str">
         <v/>
@@ -8934,7 +8934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/anakin-skywalker-ahsoka-9437.php</v>
       </c>
       <c r="L170" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/anakin-skywalker-ahsoka-9437.jpg</v>
       </c>
       <c r="M170" t="str">
         <v/>
@@ -8984,7 +8984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/night-trooper-10441.php</v>
       </c>
       <c r="L171" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/night-trooper-10441.jpg</v>
       </c>
       <c r="M171" t="str">
         <v/>
@@ -9034,7 +9034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/ezra-bridger-peridea-10442.php</v>
       </c>
       <c r="L172" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ezra-bridger-peridea-10442.jpg</v>
       </c>
       <c r="M172" t="str">
         <v/>
@@ -9084,7 +9084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/cassian-andor-aldhani-mission-5044.php</v>
       </c>
       <c r="L173" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cassian-andor-aldhani-mission-5044.jpg</v>
       </c>
       <c r="M173" t="str">
         <v/>
@@ -9134,7 +9134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/imperial-officer-dark-times-5045.php</v>
       </c>
       <c r="L174" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-officer-dark-times-5045.jpg</v>
       </c>
       <c r="M174" t="str">
         <v/>
@@ -9184,7 +9184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/shoretrooper-andor-5042.php</v>
       </c>
       <c r="L175" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/shoretrooper-andor-5042.jpg</v>
       </c>
       <c r="M175" t="str">
         <v/>
@@ -9234,7 +9234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/imperial-officer-ferrix-5043.php</v>
       </c>
       <c r="L176" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-officer-ferrix-5043.jpg</v>
       </c>
       <c r="M176" t="str">
         <v/>
@@ -9284,7 +9284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/bix-caleen-5265.php</v>
       </c>
       <c r="L177" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/bix-caleen-5265.jpg</v>
       </c>
       <c r="M177" t="str">
         <v/>
@@ -9334,7 +9334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/luthen-rael-5266.php</v>
       </c>
       <c r="L178" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luthen-rael-5266.jpg</v>
       </c>
       <c r="M178" t="str">
         <v/>
@@ -9384,7 +9384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/senator-mon-mothma-5267.php</v>
       </c>
       <c r="L179" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/senator-mon-mothma-5267.jpg</v>
       </c>
       <c r="M179" t="str">
         <v/>
@@ -9434,7 +9434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/cassian-andor-5264.php</v>
       </c>
       <c r="L180" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cassian-andor-5264.jpg</v>
       </c>
       <c r="M180" t="str">
         <v/>
@@ -9484,7 +9484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/vel-sartha-5508.php</v>
       </c>
       <c r="L181" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/vel-sartha-5508.jpg</v>
       </c>
       <c r="M181" t="str">
         <v/>
@@ -9534,7 +9534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/cassian-andor-8821.php</v>
       </c>
       <c r="L182" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cassian-andor-8821.jpg</v>
       </c>
       <c r="M182" t="str">
         <v/>
@@ -9584,7 +9584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/k-2so-andor-8820.php</v>
       </c>
       <c r="L183" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/k-2so-andor-8820.jpg</v>
       </c>
       <c r="M183" t="str">
         <v/>
@@ -9634,7 +9634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/dedra-meero-8822.php</v>
       </c>
       <c r="L184" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/dedra-meero-8822.jpg</v>
       </c>
       <c r="M184" t="str">
         <v/>
@@ -9684,7 +9684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/director-orson-krennic-andor-10262.php</v>
       </c>
       <c r="L185" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/director-orson-krennic-andor-10262.jpg</v>
       </c>
       <c r="M185" t="str">
         <v/>
@@ -9734,7 +9734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/range-trooper-andor-10691.php</v>
       </c>
       <c r="L186" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/range-trooper-andor-10691.jpg</v>
       </c>
       <c r="M186" t="str">
         <v/>
@@ -9784,7 +9784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/cassian-andor-sienar-test-pilot-10261.php</v>
       </c>
       <c r="L187" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cassian-andor-sienar-test-pilot-10261.jpg</v>
       </c>
       <c r="M187" t="str">
         <v/>
@@ -9834,7 +9834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/director-orson-krennic-dress-uniform-10717.php</v>
       </c>
       <c r="L188" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/director-orson-krennic-dress-uniform-10717.jpg</v>
       </c>
       <c r="M188" t="str">
         <v/>
@@ -9884,7 +9884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/isb-tactical-agent-10827.php</v>
       </c>
       <c r="L189" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/isb-tactical-agent-10827.jpg</v>
       </c>
       <c r="M189" t="str">
         <v/>
@@ -9934,7 +9934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/princess-leia-organa-yavin-4-3650.php</v>
       </c>
       <c r="L190" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/princess-leia-organa-yavin-4-3650.jpg</v>
       </c>
       <c r="M190" t="str">
         <v/>
@@ -9984,7 +9984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/ponda-baba-3651.php</v>
       </c>
       <c r="L191" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ponda-baba-3651.jpg</v>
       </c>
       <c r="M191" t="str">
         <v/>
@@ -10034,7 +10034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/doctor-evazan-3652.php</v>
       </c>
       <c r="L192" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/doctor-evazan-3652.jpg</v>
       </c>
       <c r="M192" t="str">
         <v/>
@@ -10084,7 +10084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/figrin-dan-4175.php</v>
       </c>
       <c r="L193" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/figrin-dan-4175.jpg</v>
       </c>
       <c r="M193" t="str">
         <v/>
@@ -10134,7 +10134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/nalan-cheel-deluxe-4177.php</v>
       </c>
       <c r="L194" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/nalan-cheel-deluxe-4177.jpg</v>
       </c>
       <c r="M194" t="str">
         <v/>
@@ -10184,7 +10184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/darth-vader-a-new-hope-7458.php</v>
       </c>
       <c r="L195" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-a-new-hope-7458.jpg</v>
       </c>
       <c r="M195" t="str">
         <v/>
@@ -10234,7 +10234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/momaw-nadon-deluxe-8451.php</v>
       </c>
       <c r="L196" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/momaw-nadon-deluxe-8451.jpg</v>
       </c>
       <c r="M196" t="str">
         <v/>
@@ -10284,7 +10284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/princess-leia-organa-8895.php</v>
       </c>
       <c r="L197" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/princess-leia-organa-8895.jpg</v>
       </c>
       <c r="M197" t="str">
         <v/>
@@ -10334,7 +10334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/luke-skywalker-8896.php</v>
       </c>
       <c r="L198" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-8896.jpg</v>
       </c>
       <c r="M198" t="str">
         <v/>
@@ -10384,7 +10384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/han-solo-10601.php</v>
       </c>
       <c r="L199" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-10601.jpg</v>
       </c>
       <c r="M199" t="str">
         <v/>
@@ -10434,7 +10434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/chewbacca-10602.php</v>
       </c>
       <c r="L200" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/chewbacca-10602.jpg</v>
       </c>
       <c r="M200" t="str">
         <v/>
@@ -10484,7 +10484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/sandtrooper-10757.php</v>
       </c>
       <c r="L201" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sandtrooper-10757.jpg</v>
       </c>
       <c r="M201" t="str">
         <v/>
@@ -10534,7 +10534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/clone-trooper-lieutenant-1460.php</v>
       </c>
       <c r="L202" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-trooper-lieutenant-1460.jpg</v>
       </c>
       <c r="M202" t="str">
         <v/>
@@ -10584,7 +10584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/phase-i-clone-trooper-1538.php</v>
       </c>
       <c r="L203" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/phase-i-clone-trooper-1538.jpg</v>
       </c>
       <c r="M203" t="str">
         <v/>
@@ -10634,7 +10634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/aayla-secura-4281.php</v>
       </c>
       <c r="L204" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/aayla-secura-4281.jpg</v>
       </c>
       <c r="M204" t="str">
         <v/>
@@ -10684,7 +10684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/ki-adi-mundi-8486.php</v>
       </c>
       <c r="L205" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ki-adi-mundi-8486.jpg</v>
       </c>
       <c r="M205" t="str">
         <v/>
@@ -10734,7 +10734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/phase-i-clone-trooper-7925.php</v>
       </c>
       <c r="L206" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/phase-i-clone-trooper-7925.jpg</v>
       </c>
       <c r="M206" t="str">
         <v/>
@@ -10784,7 +10784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/super-battle-droid-8522.php</v>
       </c>
       <c r="L207" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/super-battle-droid-8522.jpg</v>
       </c>
       <c r="M207" t="str">
         <v/>
@@ -10834,7 +10834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/luminara-unduli-9024.php</v>
       </c>
       <c r="L208" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luminara-unduli-9024.jpg</v>
       </c>
       <c r="M208" t="str">
         <v/>
@@ -10884,7 +10884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/shaak-ti-9023.php</v>
       </c>
       <c r="L209" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/shaak-ti-9023.jpg</v>
       </c>
       <c r="M209" t="str">
         <v/>
@@ -10934,7 +10934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/barriss-offee-11108.php</v>
       </c>
       <c r="L210" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/barriss-offee-11108.jpg</v>
       </c>
       <c r="M210" t="str">
         <v/>
@@ -10984,7 +10984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/jango-fett-attack-of-the-clones-11416.php</v>
       </c>
       <c r="L211" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jango-fett-attack-of-the-clones-11416.jpg</v>
       </c>
       <c r="M211" t="str">
         <v/>
@@ -11034,7 +11034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/geonosian-warrior-12857.php</v>
       </c>
       <c r="L212" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/geonosian-warrior-12857.jpg</v>
       </c>
       <c r="M212" t="str">
         <v/>
@@ -11084,7 +11084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/watto-12855.php</v>
       </c>
       <c r="L213" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/watto-12855.jpg</v>
       </c>
       <c r="M213" t="str">
         <v/>
@@ -11134,7 +11134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/taun-we-12856.php</v>
       </c>
       <c r="L214" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/taun-we-12856.jpg</v>
       </c>
       <c r="M214" t="str">
         <v/>
@@ -11184,7 +11184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/hunter-1584.php</v>
       </c>
       <c r="L215" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/hunter-1584.jpg</v>
       </c>
       <c r="M215" t="str">
         <v/>
@@ -11234,7 +11234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/crosshair-1583.php</v>
       </c>
       <c r="L216" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/crosshair-1583.jpg</v>
       </c>
       <c r="M216" t="str">
         <v/>
@@ -11284,7 +11284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/elite-squad-trooper-1645.php</v>
       </c>
       <c r="L217" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/elite-squad-trooper-1645.jpg</v>
       </c>
       <c r="M217" t="str">
         <v/>
@@ -11334,7 +11334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/tech-2080.php</v>
       </c>
       <c r="L218" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/tech-2080.jpg</v>
       </c>
       <c r="M218" t="str">
         <v/>
@@ -11384,7 +11384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/wrecker-deluxe-1872.php</v>
       </c>
       <c r="L219" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/wrecker-deluxe-1872.jpg</v>
       </c>
       <c r="M219" t="str">
         <v/>
@@ -11434,7 +11434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/clone-captain-rex-the-bad-batch-2673.php</v>
       </c>
       <c r="L220" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-captain-rex-the-bad-batch-2673.jpg</v>
       </c>
       <c r="M220" t="str">
         <v/>
@@ -11484,7 +11484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/imperial-clone-shock-trooper-2384.php</v>
       </c>
       <c r="L221" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-clone-shock-trooper-2384.jpg</v>
       </c>
       <c r="M221" t="str">
         <v/>
@@ -11534,7 +11534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/vice-admiral-rampart-2385.php</v>
       </c>
       <c r="L222" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/vice-admiral-rampart-2385.jpg</v>
       </c>
       <c r="M222" t="str">
         <v/>
@@ -11584,7 +11584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/crosshair-imperial-2674.php</v>
       </c>
       <c r="L223" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/crosshair-imperial-2674.jpg</v>
       </c>
       <c r="M223" t="str">
         <v/>
@@ -11634,7 +11634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/omega-3633.php</v>
       </c>
       <c r="L224" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/omega-3633.jpg</v>
       </c>
       <c r="M224" t="str">
         <v/>
@@ -11684,7 +11684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/echo-3634.php</v>
       </c>
       <c r="L225" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/echo-3634.jpg</v>
       </c>
       <c r="M225" t="str">
         <v/>
@@ -11734,7 +11734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/cad-bane-bracca-4011.php</v>
       </c>
       <c r="L226" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cad-bane-bracca-4011.jpg</v>
       </c>
       <c r="M226" t="str">
         <v/>
@@ -11784,7 +11784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/clone-commando-6648.php</v>
       </c>
       <c r="L227" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-commando-6648.jpg</v>
       </c>
       <c r="M227" t="str">
         <v/>
@@ -11834,7 +11834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/wrecker-mercenary-gear-6644.php</v>
       </c>
       <c r="L228" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/wrecker-mercenary-gear-6644.jpg</v>
       </c>
       <c r="M228" t="str">
         <v/>
@@ -11884,7 +11884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/hunter-mercenary-gear-6645.php</v>
       </c>
       <c r="L229" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/hunter-mercenary-gear-6645.jpg</v>
       </c>
       <c r="M229" t="str">
         <v/>
@@ -11934,7 +11934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/tech-mercenary-gear-6646.php</v>
       </c>
       <c r="L230" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/tech-mercenary-gear-6646.jpg</v>
       </c>
       <c r="M230" t="str">
         <v/>
@@ -11984,7 +11984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/echo-mercenary-gear-6647.php</v>
       </c>
       <c r="L231" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/echo-mercenary-gear-6647.jpg</v>
       </c>
       <c r="M231" t="str">
         <v/>
@@ -12034,7 +12034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/omega-mercenary-gear-6381.php</v>
       </c>
       <c r="L232" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/omega-mercenary-gear-6381.jpg</v>
       </c>
       <c r="M232" t="str">
         <v/>
@@ -12084,7 +12084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/fennec-shand-3649.php</v>
       </c>
       <c r="L233" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/fennec-shand-3649.jpg</v>
       </c>
       <c r="M233" t="str">
         <v/>
@@ -12134,7 +12134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/boba-fett-throne-room-deluxe-3730.php</v>
       </c>
       <c r="L234" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-throne-room-deluxe-3730.jpg</v>
       </c>
       <c r="M234" t="str">
         <v/>
@@ -12184,7 +12184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/luke-skywalker-grogu-6246.php</v>
       </c>
       <c r="L235" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-grogu-6246.jpg</v>
       </c>
       <c r="M235" t="str">
         <v/>
@@ -12234,7 +12234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/krrsantan-6338.php</v>
       </c>
       <c r="L236" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/krrsantan-6338.jpg</v>
       </c>
       <c r="M236" t="str">
         <v/>
@@ -12284,7 +12284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/cad-bane-bobf-6382.php</v>
       </c>
       <c r="L237" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cad-bane-bobf-6382.jpg</v>
       </c>
       <c r="M237" t="str">
         <v/>
@@ -12334,7 +12334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/tusken-chieftain-6176.php</v>
       </c>
       <c r="L238" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/tusken-chieftain-6176.jpg</v>
       </c>
       <c r="M238" t="str">
         <v/>
@@ -12384,7 +12384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/pyke-soldier-6265.php</v>
       </c>
       <c r="L239" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/pyke-soldier-6265.jpg</v>
       </c>
       <c r="M239" t="str">
         <v/>
@@ -12434,7 +12434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/the-mandalorian-glavis-ringworld-6641.php</v>
       </c>
       <c r="L240" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-mandalorian-glavis-ringworld-6641.jpg</v>
       </c>
       <c r="M240" t="str">
         <v/>
@@ -12484,7 +12484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/boba-fett-12181.php</v>
       </c>
       <c r="L241" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-12181.jpg</v>
       </c>
       <c r="M241" t="str">
         <v/>
@@ -12534,7 +12534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/mace-windu-187th-legion-clone-trooper-7463.php</v>
       </c>
       <c r="L242" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mace-windu-187th-legion-clone-trooper-7463.jpg</v>
       </c>
       <c r="M242" t="str">
         <v/>
@@ -12584,7 +12584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/yoda-clone-commander-gree-8523.php</v>
       </c>
       <c r="L243" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/yoda-clone-commander-gree-8523.jpg</v>
       </c>
       <c r="M243" t="str">
         <v/>
@@ -12634,7 +12634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/clone-trooper-kamino-1448.php</v>
       </c>
       <c r="L244" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-trooper-kamino-1448.jpg</v>
       </c>
       <c r="M244" t="str">
         <v/>
@@ -12684,7 +12684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/ahsoka-tano-clone-wars-1477.php</v>
       </c>
       <c r="L245" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ahsoka-tano-clone-wars-1477.jpg</v>
       </c>
       <c r="M245" t="str">
         <v/>
@@ -12734,7 +12734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/332nd-clone-trooper-1478.php</v>
       </c>
       <c r="L246" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/332nd-clone-trooper-1478.jpg</v>
       </c>
       <c r="M246" t="str">
         <v/>
@@ -12784,7 +12784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/mandalorian-loyalist-1480.php</v>
       </c>
       <c r="L247" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mandalorian-loyalist-1480.jpg</v>
       </c>
       <c r="M247" t="str">
         <v/>
@@ -12834,7 +12834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/mandalorian-super-commando-1479.php</v>
       </c>
       <c r="L248" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mandalorian-super-commando-1479.jpg</v>
       </c>
       <c r="M248" t="str">
         <v/>
@@ -12884,7 +12884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/cad-bane-tcw-1574.php</v>
       </c>
       <c r="L249" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cad-bane-tcw-1574.jpg</v>
       </c>
       <c r="M249" t="str">
         <v/>
@@ -12934,7 +12934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/asajj-ventress-1582.php</v>
       </c>
       <c r="L250" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/asajj-ventress-1582.jpg</v>
       </c>
       <c r="M250" t="str">
         <v/>
@@ -12984,7 +12984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/aurra-sing-2076.php</v>
       </c>
       <c r="L251" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/aurra-sing-2076.jpg</v>
       </c>
       <c r="M251" t="str">
         <v/>
@@ -13034,7 +13034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/clone-trooper-212th-battalion-2672.php</v>
       </c>
       <c r="L252" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-trooper-212th-battalion-2672.jpg</v>
       </c>
       <c r="M252" t="str">
         <v/>
@@ -13084,7 +13084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/clone-trooper-187th-battalion-4186.php</v>
       </c>
       <c r="L253" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-trooper-187th-battalion-4186.jpg</v>
       </c>
       <c r="M253" t="str">
         <v/>
@@ -13134,7 +13134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/darth-maul-cybernetic-legs-4279.php</v>
       </c>
       <c r="L254" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-maul-cybernetic-legs-4279.jpg</v>
       </c>
       <c r="M254" t="str">
         <v/>
@@ -13184,7 +13184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/clone-commander-jesse-6202.php</v>
       </c>
       <c r="L255" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-commander-jesse-6202.jpg</v>
       </c>
       <c r="M255" t="str">
         <v/>
@@ -13234,7 +13234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/ahsoka-tano-padawan-6638.php</v>
       </c>
       <c r="L256" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ahsoka-tano-padawan-6638.jpg</v>
       </c>
       <c r="M256" t="str">
         <v/>
@@ -13284,7 +13284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/phase-ii-clone-trooper-6639.php</v>
       </c>
       <c r="L257" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/phase-ii-clone-trooper-6639.jpg</v>
       </c>
       <c r="M257" t="str">
         <v/>
@@ -13334,7 +13334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/magnaguard-6640.php</v>
       </c>
       <c r="L258" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/magnaguard-6640.jpg</v>
       </c>
       <c r="M258" t="str">
         <v/>
@@ -13384,7 +13384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/arc-trooper-fives-6643.php</v>
       </c>
       <c r="L259" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/arc-trooper-fives-6643.jpg</v>
       </c>
       <c r="M259" t="str">
         <v/>
@@ -13434,7 +13434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/pre-vizsla-6955.php</v>
       </c>
       <c r="L260" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/pre-vizsla-6955.jpg</v>
       </c>
       <c r="M260" t="str">
         <v/>
@@ -13484,7 +13484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/commando-droid-8866.php</v>
       </c>
       <c r="L261" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/commando-droid-8866.jpg</v>
       </c>
       <c r="M261" t="str">
         <v/>
@@ -13534,7 +13534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/savage-opress-9006.php</v>
       </c>
       <c r="L262" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/savage-opress-9006.jpg</v>
       </c>
       <c r="M262" t="str">
         <v/>
@@ -13584,7 +13584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/jedi-temple-guard-11107.php</v>
       </c>
       <c r="L263" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jedi-temple-guard-11107.jpg</v>
       </c>
       <c r="M263" t="str">
         <v/>
@@ -13634,7 +13634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/asajj-ventress-bounty-hunter-11418.php</v>
       </c>
       <c r="L264" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/asajj-ventress-bounty-hunter-11418.jpg</v>
       </c>
       <c r="M264" t="str">
         <v/>
@@ -13684,7 +13684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/quinlan-vos-12345.php</v>
       </c>
       <c r="L265" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/quinlan-vos-12345.jpg</v>
       </c>
       <c r="M265" t="str">
         <v/>
@@ -13734,7 +13734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/darth-vader-esb-1411.php</v>
       </c>
       <c r="L266" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-esb-1411.jpg</v>
       </c>
       <c r="M266" t="str">
         <v/>
@@ -13784,7 +13784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/luke-skywalker-snowspeeder-1450.php</v>
       </c>
       <c r="L267" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-snowspeeder-1450.jpg</v>
       </c>
       <c r="M267" t="str">
         <v/>
@@ -13834,7 +13834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/rebel-trooper-hoth-1298.php</v>
       </c>
       <c r="L268" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rebel-trooper-hoth-1298.jpg</v>
       </c>
       <c r="M268" t="str">
         <v/>
@@ -13884,7 +13884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/boba-fett-prototype-armor-3802.php</v>
       </c>
       <c r="L269" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-prototype-armor-3802.jpg</v>
       </c>
       <c r="M269" t="str">
         <v/>
@@ -13934,7 +13934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/imperial-rocket-trooper-1948.php</v>
       </c>
       <c r="L270" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-rocket-trooper-1948.jpg</v>
       </c>
       <c r="M270" t="str">
         <v/>
@@ -13984,7 +13984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/cal-kestis-deluxe-1647.php</v>
       </c>
       <c r="L271" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cal-kestis-deluxe-1647.jpg</v>
       </c>
       <c r="M271" t="str">
         <v/>
@@ -14034,7 +14034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/flametrooper-2383.php</v>
       </c>
       <c r="L272" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/flametrooper-2383.jpg</v>
       </c>
       <c r="M272" t="str">
         <v/>
@@ -14084,7 +14084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/zaalbar-2632.php</v>
       </c>
       <c r="L273" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/zaalbar-2632.jpg</v>
       </c>
       <c r="M273" t="str">
         <v/>
@@ -14134,7 +14134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/nightbrother-warrior-2382.php</v>
       </c>
       <c r="L274" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/nightbrother-warrior-2382.jpg</v>
       </c>
       <c r="M274" t="str">
         <v/>
@@ -14184,7 +14184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/battlefront-ii-jet-trooper-3212.php</v>
       </c>
       <c r="L275" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/battlefront-ii-jet-trooper-3212.jpg</v>
       </c>
       <c r="M275" t="str">
         <v/>
@@ -14234,7 +14234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/rc-1138-boss-3292.php</v>
       </c>
       <c r="L276" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rc-1138-boss-3292.jpg</v>
       </c>
       <c r="M276" t="str">
         <v/>
@@ -14284,7 +14284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/imperial-senate-guard-3722.php</v>
       </c>
       <c r="L277" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-senate-guard-3722.jpg</v>
       </c>
       <c r="M277" t="str">
         <v/>
@@ -14334,7 +14334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/arc-trooper-umbra-operative-3768.php</v>
       </c>
       <c r="L278" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/arc-trooper-umbra-operative-3768.jpg</v>
       </c>
       <c r="M278" t="str">
         <v/>
@@ -14384,7 +14384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/nightbrother-archer-4021.php</v>
       </c>
       <c r="L279" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/nightbrother-archer-4021.jpg</v>
       </c>
       <c r="M279" t="str">
         <v/>
@@ -14434,7 +14434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/rc-1207-sev-4129.php</v>
       </c>
       <c r="L280" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rc-1207-sev-4129.jpg</v>
       </c>
       <c r="M280" t="str">
         <v/>
@@ -14484,7 +14484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/13th-battalion-trooper-4092.php</v>
       </c>
       <c r="L281" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/13th-battalion-trooper-4092.jpg</v>
       </c>
       <c r="M281" t="str">
         <v/>
@@ -14534,7 +14534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/rc-1140-fixer-4093.php</v>
       </c>
       <c r="L282" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rc-1140-fixer-4093.jpg</v>
       </c>
       <c r="M282" t="str">
         <v/>
@@ -14584,7 +14584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/riot-scout-trooper-4280.php</v>
       </c>
       <c r="L283" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/riot-scout-trooper-4280.jpg</v>
       </c>
       <c r="M283" t="str">
         <v/>
@@ -14634,7 +14634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/kx-security-droid-jedi-survivor-4626.php</v>
       </c>
       <c r="L284" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kx-security-droid-jedi-survivor-4626.jpg</v>
       </c>
       <c r="M284" t="str">
         <v/>
@@ -14684,7 +14684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/b1-battle-droid-jedi-survivor-4625.php</v>
       </c>
       <c r="L285" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/b1-battle-droid-jedi-survivor-4625.jpg</v>
       </c>
       <c r="M285" t="str">
         <v/>
@@ -14734,7 +14734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/cal-kestis-jedi-survivor-5451.php</v>
       </c>
       <c r="L286" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cal-kestis-jedi-survivor-5451.jpg</v>
       </c>
       <c r="M286" t="str">
         <v/>
@@ -14784,7 +14784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/rc-1262-scorch-5573.php</v>
       </c>
       <c r="L287" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rc-1262-scorch-5573.jpg</v>
       </c>
       <c r="M287" t="str">
         <v/>
@@ -14834,7 +14834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/battle-droid-republic-commando-5048.php</v>
       </c>
       <c r="L288" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/battle-droid-republic-commando-5048.jpg</v>
       </c>
       <c r="M288" t="str">
         <v/>
@@ -14884,7 +14884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/darth-malak-5504.php</v>
       </c>
       <c r="L289" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-malak-5504.jpg</v>
       </c>
       <c r="M289" t="str">
         <v/>
@@ -14934,7 +14934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/bastila-shan-5503.php</v>
       </c>
       <c r="L290" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/bastila-shan-5503.jpg</v>
       </c>
       <c r="M290" t="str">
         <v/>
@@ -14984,7 +14984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/rocket-launcher-trooper-fallen-order-5047.php</v>
       </c>
       <c r="L291" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rocket-launcher-trooper-fallen-order-5047.jpg</v>
       </c>
       <c r="M291" t="str">
         <v/>
@@ -15034,7 +15034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/darth-maul-old-master-6383.php</v>
       </c>
       <c r="L292" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-maul-old-master-6383.jpg</v>
       </c>
       <c r="M292" t="str">
         <v/>
@@ -15084,7 +15084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/darth-malgus-6635.php</v>
       </c>
       <c r="L293" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-malgus-6635.jpg</v>
       </c>
       <c r="M293" t="str">
         <v/>
@@ -15134,7 +15134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/general-grievous-battle-damaged-6642.php</v>
       </c>
       <c r="L294" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/general-grievous-battle-damaged-6642.jpg</v>
       </c>
       <c r="M294" t="str">
         <v/>
@@ -15184,7 +15184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/starkiller-the-force-unleashed-7456.php</v>
       </c>
       <c r="L295" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/starkiller-the-force-unleashed-7456.jpg</v>
       </c>
       <c r="M295" t="str">
         <v/>
@@ -15234,7 +15234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/dagan-gera-8897.php</v>
       </c>
       <c r="L296" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/dagan-gera-8897.jpg</v>
       </c>
       <c r="M296" t="str">
         <v/>
@@ -15284,7 +15284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/nightsister-merrin-10600.php</v>
       </c>
       <c r="L297" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/nightsister-merrin-10600.jpg</v>
       </c>
       <c r="M297" t="str">
         <v/>
@@ -15334,7 +15334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/kyle-katarn-dark-forces-12348.php</v>
       </c>
       <c r="L298" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kyle-katarn-dark-forces-12348.jpg</v>
       </c>
       <c r="M298" t="str">
         <v/>
@@ -15384,7 +15384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/lord-starkiller-12921.php</v>
       </c>
       <c r="L299" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/lord-starkiller-12921.jpg</v>
       </c>
       <c r="M299" t="str">
         <v/>
@@ -15434,7 +15434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/the-armorer-deluxe-1543.php</v>
       </c>
       <c r="L300" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-armorer-deluxe-1543.jpg</v>
       </c>
       <c r="M300" t="str">
         <v/>
@@ -15484,7 +15484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/speeder-bike-scout-trooper-and-the-child-1580.php</v>
       </c>
       <c r="L301" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/speeder-bike-scout-trooper-and-the-child-1580.jpg</v>
       </c>
       <c r="M301" t="str">
         <v/>
@@ -15534,7 +15534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/paz-vizsla-deluxe-2874.php</v>
       </c>
       <c r="L302" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/paz-vizsla-deluxe-2874.jpg</v>
       </c>
       <c r="M302" t="str">
         <v/>
@@ -15584,7 +15584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/scout-trooper-carbonized-2875.php</v>
       </c>
       <c r="L303" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/scout-trooper-carbonized-2875.jpg</v>
       </c>
       <c r="M303" t="str">
         <v/>
@@ -15634,7 +15634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/shoretrooper-carbonized-2876.php</v>
       </c>
       <c r="L304" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/shoretrooper-carbonized-2876.jpg</v>
       </c>
       <c r="M304" t="str">
         <v/>
@@ -15684,7 +15684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/mandalorian-beskar-armor-1412.php</v>
       </c>
       <c r="L305" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mandalorian-beskar-armor-1412.jpg</v>
       </c>
       <c r="M305" t="str">
         <v/>
@@ -15734,7 +15734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/imperial-stormtrooper-mandalorian-1449.php</v>
       </c>
       <c r="L306" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-stormtrooper-mandalorian-1449.jpg</v>
       </c>
       <c r="M306" t="str">
         <v/>
@@ -15784,7 +15784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/incinerator-trooper-1537.php</v>
       </c>
       <c r="L307" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/incinerator-trooper-1537.jpg</v>
       </c>
       <c r="M307" t="str">
         <v/>
@@ -15834,7 +15834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/the-armorer-1570.php</v>
       </c>
       <c r="L308" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-armorer-1570.jpg</v>
       </c>
       <c r="M308" t="str">
         <v/>
@@ -15884,7 +15884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/din-djarin-and-the-child-deluxe-1579.php</v>
       </c>
       <c r="L309" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/din-djarin-and-the-child-deluxe-1579.jpg</v>
       </c>
       <c r="M309" t="str">
         <v/>
@@ -15934,7 +15934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/greef-karga-1595.php</v>
       </c>
       <c r="L310" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/greef-karga-1595.jpg</v>
       </c>
       <c r="M310" t="str">
         <v/>
@@ -15984,7 +15984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/kuiil-1594.php</v>
       </c>
       <c r="L311" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kuiil-1594.jpg</v>
       </c>
       <c r="M311" t="str">
         <v/>
@@ -16034,7 +16034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/moff-gideon-1596.php</v>
       </c>
       <c r="L312" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/moff-gideon-1596.jpg</v>
       </c>
       <c r="M312" t="str">
         <v/>
@@ -16084,7 +16084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/remnant-stormtrooper-1585.php</v>
       </c>
       <c r="L313" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/remnant-stormtrooper-1585.jpg</v>
       </c>
       <c r="M313" t="str">
         <v/>
@@ -16134,7 +16134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/bo-katan-kryze-1615.php</v>
       </c>
       <c r="L314" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/bo-katan-kryze-1615.jpg</v>
       </c>
       <c r="M314" t="str">
         <v/>
@@ -16184,7 +16184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/q9-0-zero-2079.php</v>
       </c>
       <c r="L315" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/q9-0-zero-2079.jpg</v>
       </c>
       <c r="M315" t="str">
         <v/>
@@ -16234,7 +16234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/koska-reeves-2078.php</v>
       </c>
       <c r="L316" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/koska-reeves-2078.jpg</v>
       </c>
       <c r="M316" t="str">
         <v/>
@@ -16284,7 +16284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/artillery-stormtrooper-3414.php</v>
       </c>
       <c r="L317" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/artillery-stormtrooper-3414.jpg</v>
       </c>
       <c r="M317" t="str">
         <v/>
@@ -16334,7 +16334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/the-mandalorian-and-grogu-arvala-7-deluxe-1228.php</v>
       </c>
       <c r="L318" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-mandalorian-and-grogu-arvala-7-deluxe-1228.jpg</v>
       </c>
       <c r="M318" t="str">
         <v/>
@@ -16384,7 +16384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/migs-mayfeld-morak-3540.php</v>
       </c>
       <c r="L319" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/migs-mayfeld-morak-3540.jpg</v>
       </c>
       <c r="M319" t="str">
         <v/>
@@ -16434,7 +16434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/boba-fett-tython-3539.php</v>
       </c>
       <c r="L320" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-tython-3539.jpg</v>
       </c>
       <c r="M320" t="str">
         <v/>
@@ -16484,7 +16484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/the-mandalorian-grogu-maldo-kreis-deluxe-3529.php</v>
       </c>
       <c r="L321" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-mandalorian-grogu-maldo-kreis-deluxe-3529.jpg</v>
       </c>
       <c r="M321" t="str">
         <v/>
@@ -16534,7 +16534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/cobb-vanth-deluxe-3530.php</v>
       </c>
       <c r="L322" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cobb-vanth-deluxe-3530.jpg</v>
       </c>
       <c r="M322" t="str">
         <v/>
@@ -16584,7 +16584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/ahsoka-tano-corvus-3914.php</v>
       </c>
       <c r="L323" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ahsoka-tano-corvus-3914.jpg</v>
       </c>
       <c r="M323" t="str">
         <v/>
@@ -16634,7 +16634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/the-client-3629.php</v>
       </c>
       <c r="L324" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-client-3629.jpg</v>
       </c>
       <c r="M324" t="str">
         <v/>
@@ -16684,7 +16684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/death-watch-mandalorian-3915.php</v>
       </c>
       <c r="L325" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/death-watch-mandalorian-3915.jpg</v>
       </c>
       <c r="M325" t="str">
         <v/>
@@ -16734,7 +16734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/boba-fett-tython-jedi-ruins-deluxe-3948.php</v>
       </c>
       <c r="L326" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-tython-jedi-ruins-deluxe-3948.jpg</v>
       </c>
       <c r="M326" t="str">
         <v/>
@@ -16784,7 +16784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/new-republic-security-droid-4176.php</v>
       </c>
       <c r="L327" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/new-republic-security-droid-4176.jpg</v>
       </c>
       <c r="M327" t="str">
         <v/>
@@ -16834,7 +16834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/magistrate-greef-karga-4278.php</v>
       </c>
       <c r="L328" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/magistrate-greef-karga-4278.jpg</v>
       </c>
       <c r="M328" t="str">
         <v/>
@@ -16884,7 +16884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/axe-woves-4612.php</v>
       </c>
       <c r="L329" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/axe-woves-4612.jpg</v>
       </c>
       <c r="M329" t="str">
         <v/>
@@ -16934,7 +16934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/grogu-4597.php</v>
       </c>
       <c r="L330" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/grogu-4597.jpg</v>
       </c>
       <c r="M330" t="str">
         <v/>
@@ -16984,7 +16984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/migs-mayfeld-4598.php</v>
       </c>
       <c r="L331" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/migs-mayfeld-4598.jpg</v>
       </c>
       <c r="M331" t="str">
         <v/>
@@ -17034,7 +17034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/dark-trooper-deluxe-3946.php</v>
       </c>
       <c r="L332" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/dark-trooper-deluxe-3946.jpg</v>
       </c>
       <c r="M332" t="str">
         <v/>
@@ -17084,7 +17084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/hk-87-4599.php</v>
       </c>
       <c r="L333" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/hk-87-4599.jpg</v>
       </c>
       <c r="M333" t="str">
         <v/>
@@ -17134,7 +17134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/luke-skywalker-imperial-light-cruiser-4600.php</v>
       </c>
       <c r="L334" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-imperial-light-cruiser-4600.jpg</v>
       </c>
       <c r="M334" t="str">
         <v/>
@@ -17184,7 +17184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/din-djarin-morak-5450.php</v>
       </c>
       <c r="L335" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/din-djarin-morak-5450.jpg</v>
       </c>
       <c r="M335" t="str">
         <v/>
@@ -17234,7 +17234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/r2-d2-the-mandalorian-6954.php</v>
       </c>
       <c r="L336" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/r2-d2-the-mandalorian-6954.jpg</v>
       </c>
       <c r="M336" t="str">
         <v/>
@@ -17284,7 +17284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/r5-d4-mandalorian-6432.php</v>
       </c>
       <c r="L337" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/r5-d4-mandalorian-6432.jpg</v>
       </c>
       <c r="M337" t="str">
         <v/>
@@ -17334,7 +17334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/mandalorian-fleet-commander-6443.php</v>
       </c>
       <c r="L338" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mandalorian-fleet-commander-6443.jpg</v>
       </c>
       <c r="M338" t="str">
         <v/>
@@ -17384,7 +17384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/r4-6d0-7459.php</v>
       </c>
       <c r="L339" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/r4-6d0-7459.jpg</v>
       </c>
       <c r="M339" t="str">
         <v/>
@@ -17434,7 +17434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/paz-vizsla-7462.php</v>
       </c>
       <c r="L340" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/paz-vizsla-7462.jpg</v>
       </c>
       <c r="M340" t="str">
         <v/>
@@ -17484,7 +17484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/the-mandalorian-mines-of-mandalore-7457.php</v>
       </c>
       <c r="L341" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-mandalorian-mines-of-mandalore-7457.jpg</v>
       </c>
       <c r="M341" t="str">
         <v/>
@@ -17534,7 +17534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/mandalorian-nite-owl-8118.php</v>
       </c>
       <c r="L342" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mandalorian-nite-owl-8118.jpg</v>
       </c>
       <c r="M342" t="str">
         <v/>
@@ -17584,7 +17584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/mandalorian-privateer-8485.php</v>
       </c>
       <c r="L343" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mandalorian-privateer-8485.jpg</v>
       </c>
       <c r="M343" t="str">
         <v/>
@@ -17634,7 +17634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/mandalorian-shriek-hawk-8693.php</v>
       </c>
       <c r="L344" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mandalorian-shriek-hawk-8693.jpg</v>
       </c>
       <c r="M344" t="str">
         <v/>
@@ -17684,7 +17684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/ig-12-grogu-deluxe-8779.php</v>
       </c>
       <c r="L345" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ig-12-grogu-deluxe-8779.jpg</v>
       </c>
       <c r="M345" t="str">
         <v/>
@@ -17734,7 +17734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/imperial-armored-commando-8780.php</v>
       </c>
       <c r="L346" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-armored-commando-8780.jpg</v>
       </c>
       <c r="M346" t="str">
         <v/>
@@ -17784,7 +17784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/imperial-praetorian-guard-10263.php</v>
       </c>
       <c r="L347" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-praetorian-guard-10263.jpg</v>
       </c>
       <c r="M347" t="str">
         <v/>
@@ -17834,7 +17834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/moff-gideon-dark-trooper-armor-10264.php</v>
       </c>
       <c r="L348" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/moff-gideon-dark-trooper-armor-10264.jpg</v>
       </c>
       <c r="M348" t="str">
         <v/>
@@ -17884,7 +17884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/the-mandalorian-pagodon-12513.php</v>
       </c>
       <c r="L349" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-mandalorian-pagodon-12513.jpg</v>
       </c>
       <c r="M349" t="str">
         <v/>
@@ -17934,7 +17934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/the-mandalorian-grogu-first-edition-deluxe-12990.php</v>
       </c>
       <c r="L350" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-mandalorian-grogu-first-edition-deluxe-12990.jpg</v>
       </c>
       <c r="M350" t="str">
         <v/>
@@ -17984,7 +17984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/the-mandalorian-grogu-deluxe-12987.php</v>
       </c>
       <c r="L351" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-mandalorian-grogu-deluxe-12987.jpg</v>
       </c>
       <c r="M351" t="str">
         <v/>
@@ -18034,7 +18034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/remnant-at-at-driver-12984.php</v>
       </c>
       <c r="L352" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/remnant-at-at-driver-12984.jpg</v>
       </c>
       <c r="M352" t="str">
         <v/>
@@ -18084,7 +18084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/remnant-at-at-driver-first-edition-12993.php</v>
       </c>
       <c r="L353" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/remnant-at-at-driver-first-edition-12993.jpg</v>
       </c>
       <c r="M353" t="str">
         <v/>
@@ -18134,7 +18134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/imperial-remnant-at-rt-driver-first-edition-12992.php</v>
       </c>
       <c r="L354" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-remnant-at-rt-driver-first-edition-12992.jpg</v>
       </c>
       <c r="M354" t="str">
         <v/>
@@ -18184,7 +18184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/imperial-remnant-at-rt-driver-12985.php</v>
       </c>
       <c r="L355" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-remnant-at-rt-driver-12985.jpg</v>
       </c>
       <c r="M355" t="str">
         <v/>
@@ -18234,7 +18234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/colonel-ward-12988.php</v>
       </c>
       <c r="L356" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/colonel-ward-12988.jpg</v>
       </c>
       <c r="M356" t="str">
         <v/>
@@ -18284,7 +18284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/colonel-ward-first-edition-12989.php</v>
       </c>
       <c r="L357" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/colonel-ward-first-edition-12989.jpg</v>
       </c>
       <c r="M357" t="str">
         <v/>
@@ -18334,7 +18334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/imperial-remnant-stormtrooper-12986.php</v>
       </c>
       <c r="L358" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-remnant-stormtrooper-12986.jpg</v>
       </c>
       <c r="M358" t="str">
         <v/>
@@ -18384,7 +18384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/imperial-remnant-stormtrooper-first-edition-12991.php</v>
       </c>
       <c r="L359" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-remnant-stormtrooper-first-edition-12991.jpg</v>
       </c>
       <c r="M359" t="str">
         <v/>
@@ -18434,7 +18434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/imperial-remnant-stormtrooper-brown-leg-13169.php</v>
       </c>
       <c r="L360" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-remnant-stormtrooper-brown-leg-13169.jpg</v>
       </c>
       <c r="M360" t="str">
         <v/>
@@ -18484,7 +18484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/maul-13121.php</v>
       </c>
       <c r="L361" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/maul-13121.jpg</v>
       </c>
       <c r="M361" t="str">
         <v/>
@@ -18534,7 +18534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/rook-kast-13122.php</v>
       </c>
       <c r="L362" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rook-kast-13122.jpg</v>
       </c>
       <c r="M362" t="str">
         <v/>
@@ -18584,7 +18584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/eleventh-brother-13123.php</v>
       </c>
       <c r="L363" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/eleventh-brother-13123.jpg</v>
       </c>
       <c r="M363" t="str">
         <v/>
@@ -18634,7 +18634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/devon-izara-13124.php</v>
       </c>
       <c r="L364" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/devon-izara-13124.jpg</v>
       </c>
       <c r="M364" t="str">
         <v/>
@@ -18684,7 +18684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/obi-wan-kenobi-wandering-jedi-4188.php</v>
       </c>
       <c r="L365" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-wandering-jedi-4188.jpg</v>
       </c>
       <c r="M365" t="str">
         <v/>
@@ -18734,7 +18734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/darth-vader-obi-wan-kenobi-4291.php</v>
       </c>
       <c r="L366" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-obi-wan-kenobi-4291.jpg</v>
       </c>
       <c r="M366" t="str">
         <v/>
@@ -18784,7 +18784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/reva-third-sister-4261.php</v>
       </c>
       <c r="L367" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/reva-third-sister-4261.jpg</v>
       </c>
       <c r="M367" t="str">
         <v/>
@@ -18834,7 +18834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/fifth-brother-inquisitor-4266.php</v>
       </c>
       <c r="L368" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/fifth-brother-inquisitor-4266.jpg</v>
       </c>
       <c r="M368" t="str">
         <v/>
@@ -18884,7 +18884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/teeka-jawa-4327.php</v>
       </c>
       <c r="L369" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/teeka-jawa-4327.jpg</v>
       </c>
       <c r="M369" t="str">
         <v/>
@@ -18934,7 +18934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/ben-kenobi-tibidon-station-4292.php</v>
       </c>
       <c r="L370" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ben-kenobi-tibidon-station-4292.jpg</v>
       </c>
       <c r="M370" t="str">
         <v/>
@@ -18984,7 +18984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/purge-trooper-phase-ii-armor-4334.php</v>
       </c>
       <c r="L371" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/purge-trooper-phase-ii-armor-4334.jpg</v>
       </c>
       <c r="M371" t="str">
         <v/>
@@ -19034,7 +19034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/1-jac-4335.php</v>
       </c>
       <c r="L372" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/1-jac-4335.jpg</v>
       </c>
       <c r="M372" t="str">
         <v/>
@@ -19084,7 +19084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/grand-inquisitor-4265.php</v>
       </c>
       <c r="L373" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/grand-inquisitor-4265.jpg</v>
       </c>
       <c r="M373" t="str">
         <v/>
@@ -19134,7 +19134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/ned-b-deluxe-4317.php</v>
       </c>
       <c r="L374" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ned-b-deluxe-4317.jpg</v>
       </c>
       <c r="M374" t="str">
         <v/>
@@ -19184,7 +19184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/obi-wan-kenobi-jabiim-4326.php</v>
       </c>
       <c r="L375" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-jabiim-4326.jpg</v>
       </c>
       <c r="M375" t="str">
         <v/>
@@ -19234,7 +19234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/fourth-sister-inquisitor-4268.php</v>
       </c>
       <c r="L376" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/fourth-sister-inquisitor-4268.jpg</v>
       </c>
       <c r="M376" t="str">
         <v/>
@@ -19284,7 +19284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/tala-imperial-officer-4336.php</v>
       </c>
       <c r="L377" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/tala-imperial-officer-4336.jpg</v>
       </c>
       <c r="M377" t="str">
         <v/>
@@ -19334,7 +19334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/commander-appo-6881.php</v>
       </c>
       <c r="L378" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/commander-appo-6881.jpg</v>
       </c>
       <c r="M378" t="str">
         <v/>
@@ -19384,7 +19384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/darth-vader-duels-end-6882.php</v>
       </c>
       <c r="L379" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-duels-end-6882.jpg</v>
       </c>
       <c r="M379" t="str">
         <v/>
@@ -19434,7 +19434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/darth-vader-reissue-duels-end-12182.php</v>
       </c>
       <c r="L380" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-reissue-duels-end-12182.jpg</v>
       </c>
       <c r="M380" t="str">
         <v/>
@@ -19484,7 +19484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/qui-gon-jinn-force-spirit-6886.php</v>
       </c>
       <c r="L381" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/qui-gon-jinn-force-spirit-6886.jpg</v>
       </c>
       <c r="M381" t="str">
         <v/>
@@ -19534,7 +19534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/obi-wan-kenobi-jedi-legend-6887.php</v>
       </c>
       <c r="L382" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-jedi-legend-6887.jpg</v>
       </c>
       <c r="M382" t="str">
         <v/>
@@ -19584,7 +19584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/garazeb-zeb-orrelios-deluxe-1441.php</v>
       </c>
       <c r="L383" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/garazeb-zeb-orrelios-deluxe-1441.jpg</v>
       </c>
       <c r="M383" t="str">
         <v/>
@@ -19634,7 +19634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/chopper-1442.php</v>
       </c>
       <c r="L384" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/chopper-1442.jpg</v>
       </c>
       <c r="M384" t="str">
         <v/>
@@ -19684,7 +19684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/ezra-bridger-1443.php</v>
       </c>
       <c r="L385" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ezra-bridger-1443.jpg</v>
       </c>
       <c r="M385" t="str">
         <v/>
@@ -19734,7 +19734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/kanan-jarrus-rebels-1444.php</v>
       </c>
       <c r="L386" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kanan-jarrus-rebels-1444.jpg</v>
       </c>
       <c r="M386" t="str">
         <v/>
@@ -19784,7 +19784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/hera-syndulla-1445.php</v>
       </c>
       <c r="L387" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/hera-syndulla-1445.jpg</v>
       </c>
       <c r="M387" t="str">
         <v/>
@@ -19834,7 +19834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/sabine-wren-1446.php</v>
       </c>
       <c r="L388" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sabine-wren-1446.jpg</v>
       </c>
       <c r="M388" t="str">
         <v/>
@@ -19884,7 +19884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/ahsoka-tano-rebels-1447.php</v>
       </c>
       <c r="L389" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ahsoka-tano-rebels-1447.jpg</v>
       </c>
       <c r="M389" t="str">
         <v/>
@@ -19934,7 +19934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/chopper-c1-10p-repack-7203.php</v>
       </c>
       <c r="L390" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/chopper-c1-10p-repack-7203.jpg</v>
       </c>
       <c r="M390" t="str">
         <v/>
@@ -19984,7 +19984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/seventh-sister-inquisitor-12347.php</v>
       </c>
       <c r="L391" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/seventh-sister-inquisitor-12347.jpg</v>
       </c>
       <c r="M391" t="str">
         <v/>
@@ -20034,7 +20034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/jyn-erso-2524.php</v>
       </c>
       <c r="L392" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jyn-erso-2524.jpg</v>
       </c>
       <c r="M392" t="str">
         <v/>
@@ -20084,7 +20084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/captain-cassian-andor-2522.php</v>
       </c>
       <c r="L393" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/captain-cassian-andor-2522.jpg</v>
       </c>
       <c r="M393" t="str">
         <v/>
@@ -20134,7 +20134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/k-2so-2525.php</v>
       </c>
       <c r="L394" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/k-2so-2525.jpg</v>
       </c>
       <c r="M394" t="str">
         <v/>
@@ -20184,7 +20184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/chirrut-imwe-2523.php</v>
       </c>
       <c r="L395" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/chirrut-imwe-2523.jpg</v>
       </c>
       <c r="M395" t="str">
         <v/>
@@ -20234,7 +20234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/baze-malbus-rogue-one-2520.php</v>
       </c>
       <c r="L396" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/baze-malbus-rogue-one-2520.jpg</v>
       </c>
       <c r="M396" t="str">
         <v/>
@@ -20284,7 +20284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/bodhi-rook-2521.php</v>
       </c>
       <c r="L397" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/bodhi-rook-2521.jpg</v>
       </c>
       <c r="M397" t="str">
         <v/>
@@ -20334,7 +20334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/galen-erso-2518.php</v>
       </c>
       <c r="L398" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/galen-erso-2518.jpg</v>
       </c>
       <c r="M398" t="str">
         <v/>
@@ -20384,7 +20384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/antoc-merrick-2519.php</v>
       </c>
       <c r="L399" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/antoc-merrick-2519.jpg</v>
       </c>
       <c r="M399" t="str">
         <v/>
@@ -20434,7 +20434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/stormtrooper-jedha-patrol-3632.php</v>
       </c>
       <c r="L400" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/stormtrooper-jedha-patrol-3632.jpg</v>
       </c>
       <c r="M400" t="str">
         <v/>
@@ -20484,7 +20484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/saw-gerrera-deluxe-4125.php</v>
       </c>
       <c r="L401" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/saw-gerrera-deluxe-4125.jpg</v>
       </c>
       <c r="M401" t="str">
         <v/>
@@ -20534,7 +20534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/admiral-ackbar-1409.php</v>
       </c>
       <c r="L402" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/admiral-ackbar-1409.jpg</v>
       </c>
       <c r="M402" t="str">
         <v/>
@@ -20584,7 +20584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/teebo-1410.php</v>
       </c>
       <c r="L403" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/teebo-1410.jpg</v>
       </c>
       <c r="M403" t="str">
         <v/>
@@ -20634,7 +20634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/princess-leia-organa-endor-1571.php</v>
       </c>
       <c r="L404" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/princess-leia-organa-endor-1571.jpg</v>
       </c>
       <c r="M404" t="str">
         <v/>
@@ -20684,7 +20684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/luke-skywalker-endor-1572.php</v>
       </c>
       <c r="L405" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-endor-1572.jpg</v>
       </c>
       <c r="M405" t="str">
         <v/>
@@ -20734,7 +20734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/han-solo-endor-1573.php</v>
       </c>
       <c r="L406" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-endor-1573.jpg</v>
       </c>
       <c r="M406" t="str">
         <v/>
@@ -20784,7 +20784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/boba-fett-rotj-deluxe-1540.php</v>
       </c>
       <c r="L407" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-rotj-deluxe-1540.jpg</v>
       </c>
       <c r="M407" t="str">
         <v/>
@@ -20834,7 +20834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/general-lando-calrissian-2077.php</v>
       </c>
       <c r="L408" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/general-lando-calrissian-2077.jpg</v>
       </c>
       <c r="M408" t="str">
         <v/>
@@ -20884,7 +20884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/bib-fortuna-3635.php</v>
       </c>
       <c r="L409" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/bib-fortuna-3635.jpg</v>
       </c>
       <c r="M409" t="str">
         <v/>
@@ -20934,7 +20934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/princess-leia-ewok-village-4174.php</v>
       </c>
       <c r="L410" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/princess-leia-ewok-village-4174.jpg</v>
       </c>
       <c r="M410" t="str">
         <v/>
@@ -20984,7 +20984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/chewbacca-rotj-6637.php</v>
       </c>
       <c r="L411" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/chewbacca-rotj-6637.jpg</v>
       </c>
       <c r="M411" t="str">
         <v/>
@@ -21034,7 +21034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/wicket-w-warrick-6636.php</v>
       </c>
       <c r="L412" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/wicket-w-warrick-6636.jpg</v>
       </c>
       <c r="M412" t="str">
         <v/>
@@ -21084,7 +21084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/darth-sidious-8521.php</v>
       </c>
       <c r="L413" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-sidious-8521.jpg</v>
       </c>
       <c r="M413" t="str">
         <v/>
@@ -21134,7 +21134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/clone-commander-bacara-8865.php</v>
       </c>
       <c r="L414" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-commander-bacara-8865.jpg</v>
       </c>
       <c r="M414" t="str">
         <v/>
@@ -21184,7 +21184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/clone-lieutenant-galle-10756.php</v>
       </c>
       <c r="L415" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-lieutenant-galle-10756.jpg</v>
       </c>
       <c r="M415" t="str">
         <v/>
@@ -21234,7 +21234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/obi-wan-kenobi-revenge-of-the-sith-11875.php</v>
       </c>
       <c r="L416" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-revenge-of-the-sith-11875.jpg</v>
       </c>
       <c r="M416" t="str">
         <v/>
@@ -21284,7 +21284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/anakin-skywalker-revenge-of-the-sith-11874.php</v>
       </c>
       <c r="L417" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/anakin-skywalker-revenge-of-the-sith-11874.jpg</v>
       </c>
       <c r="M417" t="str">
         <v/>
@@ -21334,7 +21334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/jod-na-nawood-9035.php</v>
       </c>
       <c r="L418" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jod-na-nawood-9035.jpg</v>
       </c>
       <c r="M418" t="str">
         <v/>
@@ -21384,7 +21384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/neel-at-attin-9039.php</v>
       </c>
       <c r="L419" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/neel-at-attin-9039.jpg</v>
       </c>
       <c r="M419" t="str">
         <v/>
@@ -21434,7 +21434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/wim-at-attin-9036.php</v>
       </c>
       <c r="L420" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/wim-at-attin-9036.jpg</v>
       </c>
       <c r="M420" t="str">
         <v/>
@@ -21484,7 +21484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/fern-at-attin-9037.php</v>
       </c>
       <c r="L421" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/fern-at-attin-9037.jpg</v>
       </c>
       <c r="M421" t="str">
         <v/>
@@ -21534,7 +21534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/kb-at-attin-9038.php</v>
       </c>
       <c r="L422" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kb-at-attin-9038.jpg</v>
       </c>
       <c r="M422" t="str">
         <v/>
@@ -21584,7 +21584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/captain-brutus-port-borgo-9034.php</v>
       </c>
       <c r="L423" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/captain-brutus-port-borgo-9034.jpg</v>
       </c>
       <c r="M423" t="str">
         <v/>
@@ -21634,7 +21634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/sm-33-deluxe-10443.php</v>
       </c>
       <c r="L424" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sm-33-deluxe-10443.jpg</v>
       </c>
       <c r="M424" t="str">
         <v/>
@@ -21684,7 +21684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/prince-xizor-8864.php</v>
       </c>
       <c r="L425" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/prince-xizor-8864.jpg</v>
       </c>
       <c r="M425" t="str">
         <v/>
@@ -21734,7 +21734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/dash-rendar-10599.php</v>
       </c>
       <c r="L426" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/dash-rendar-10599.jpg</v>
       </c>
       <c r="M426" t="str">
         <v/>
@@ -21784,7 +21784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/osha-aniseya-8591.php</v>
       </c>
       <c r="L427" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/osha-aniseya-8591.jpg</v>
       </c>
       <c r="M427" t="str">
         <v/>
@@ -21834,7 +21834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/jedi-master-sol-8341.php</v>
       </c>
       <c r="L428" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jedi-master-sol-8341.jpg</v>
       </c>
       <c r="M428" t="str">
         <v/>
@@ -21884,7 +21884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/padawan-jecki-lon-8342.php</v>
       </c>
       <c r="L429" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/padawan-jecki-lon-8342.jpg</v>
       </c>
       <c r="M429" t="str">
         <v/>
@@ -21934,7 +21934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/jedi-knight-yord-fandar-8343.php</v>
       </c>
       <c r="L430" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jedi-knight-yord-fandar-8343.jpg</v>
       </c>
       <c r="M430" t="str">
         <v/>
@@ -21984,7 +21984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/jedi-master-indara-8344.php</v>
       </c>
       <c r="L431" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jedi-master-indara-8344.jpg</v>
       </c>
       <c r="M431" t="str">
         <v/>
@@ -22034,7 +22034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/mae-assassin-8345.php</v>
       </c>
       <c r="L432" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mae-assassin-8345.jpg</v>
       </c>
       <c r="M432" t="str">
         <v/>
@@ -22084,7 +22084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/bazil-jedi-order-tracker-8782.php</v>
       </c>
       <c r="L433" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/bazil-jedi-order-tracker-8782.jpg</v>
       </c>
       <c r="M433" t="str">
         <v/>
@@ -22134,7 +22134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/jedi-master-vernestra-rwoh-8783.php</v>
       </c>
       <c r="L434" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jedi-master-vernestra-rwoh-8783.jpg</v>
       </c>
       <c r="M434" t="str">
         <v/>
@@ -22184,7 +22184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/jedi-master-kelnacca-deluxe-9071.php</v>
       </c>
       <c r="L435" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jedi-master-kelnacca-deluxe-9071.jpg</v>
       </c>
       <c r="M435" t="str">
         <v/>
@@ -22234,7 +22234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/the-stranger-qimir-11417.php</v>
       </c>
       <c r="L436" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-stranger-qimir-11417.jpg</v>
       </c>
       <c r="M436" t="str">
         <v/>
@@ -22284,7 +22284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/jar-jar-binks-deluxe-1539.php</v>
       </c>
       <c r="L437" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jar-jar-binks-deluxe-1539.jpg</v>
       </c>
       <c r="M437" t="str">
         <v/>
@@ -22334,7 +22334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/anakin-skywalker-7475.php</v>
       </c>
       <c r="L438" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/anakin-skywalker-7475.jpg</v>
       </c>
       <c r="M438" t="str">
         <v/>
@@ -22384,7 +22384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/padme-amidala-7474.php</v>
       </c>
       <c r="L439" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/padme-amidala-7474.jpg</v>
       </c>
       <c r="M439" t="str">
         <v/>
@@ -22434,7 +22434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/droideka-destroyer-droid-7926.php</v>
       </c>
       <c r="L440" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/droideka-destroyer-droid-7926.jpg</v>
       </c>
       <c r="M440" t="str">
         <v/>
@@ -22484,7 +22484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/darth-maul-8823.php</v>
       </c>
       <c r="L441" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-maul-8823.jpg</v>
       </c>
       <c r="M441" t="str">
         <v/>
@@ -22534,7 +22534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/sebulba-9025.php</v>
       </c>
       <c r="L442" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sebulba-9025.jpg</v>
       </c>
       <c r="M442" t="str">
         <v/>
@@ -22584,7 +22584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/rey-dark-side-vision-1536.php</v>
       </c>
       <c r="L443" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rey-dark-side-vision-1536.jpg</v>
       </c>
       <c r="M443" t="str">
         <v/>
@@ -22634,7 +22634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/the-ronin-11109.php</v>
       </c>
       <c r="L444" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-ronin-11109.jpg</v>
       </c>
       <c r="M444" t="str">
         <v/>
@@ -22684,7 +22684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxy/jedi-master-dooku-12346.php</v>
       </c>
       <c r="L445" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jedi-master-dooku-12346.jpg</v>
       </c>
       <c r="M445" t="str">
         <v/>
@@ -22734,7 +22734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/darth-vader-legacy-pack-276.php</v>
       </c>
       <c r="L446" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-legacy-pack-276.jpg</v>
       </c>
       <c r="M446" t="str">
         <v/>
@@ -22784,7 +22784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/luke-skywalker-x-wing-pilot-274.php</v>
       </c>
       <c r="L447" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-x-wing-pilot-274.jpg</v>
       </c>
       <c r="M447" t="str">
         <v/>
@@ -22834,7 +22834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/r5-d4-273.php</v>
       </c>
       <c r="L448" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/r5-d4-273.jpg</v>
       </c>
       <c r="M448" t="str">
         <v/>
@@ -22884,7 +22884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/han-solo-anh-280.php</v>
       </c>
       <c r="L449" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-anh-280.jpg</v>
       </c>
       <c r="M449" t="str">
         <v/>
@@ -22934,7 +22934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/luke-skywalker-anh-269.php</v>
       </c>
       <c r="L450" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-anh-269.jpg</v>
       </c>
       <c r="M450" t="str">
         <v/>
@@ -22984,7 +22984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/obi-wan-kenobi-271.php</v>
       </c>
       <c r="L451" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-271.jpg</v>
       </c>
       <c r="M451" t="str">
         <v/>
@@ -23034,7 +23034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/princess-leia-organa-anh-270.php</v>
       </c>
       <c r="L452" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/princess-leia-organa-anh-270.jpg</v>
       </c>
       <c r="M452" t="str">
         <v/>
@@ -23084,7 +23084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/r2-d2-anh-278.php</v>
       </c>
       <c r="L453" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/r2-d2-anh-278.jpg</v>
       </c>
       <c r="M453" t="str">
         <v/>
@@ -23134,7 +23134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/tusken-raider-279.php</v>
       </c>
       <c r="L454" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/tusken-raider-279.jpg</v>
       </c>
       <c r="M454" t="str">
         <v/>
@@ -23184,7 +23184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/c-3po-281.php</v>
       </c>
       <c r="L455" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/c-3po-281.jpg</v>
       </c>
       <c r="M455" t="str">
         <v/>
@@ -23234,7 +23234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/chewbacca-anh-268.php</v>
       </c>
       <c r="L456" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/chewbacca-anh-268.jpg</v>
       </c>
       <c r="M456" t="str">
         <v/>
@@ -23284,7 +23284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/death-squad-commander-272.php</v>
       </c>
       <c r="L457" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/death-squad-commander-272.jpg</v>
       </c>
       <c r="M457" t="str">
         <v/>
@@ -23334,7 +23334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/jawa-277.php</v>
       </c>
       <c r="L458" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jawa-277.jpg</v>
       </c>
       <c r="M458" t="str">
         <v/>
@@ -23384,7 +23384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/stormtrooper-287.php</v>
       </c>
       <c r="L459" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/stormtrooper-287.jpg</v>
       </c>
       <c r="M459" t="str">
         <v/>
@@ -23434,7 +23434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/boba-fett-sdcc-esb-1248.php</v>
       </c>
       <c r="L460" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-sdcc-esb-1248.jpg</v>
       </c>
       <c r="M460" t="str">
         <v/>
@@ -23484,7 +23484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/4-lom-zuckuss-2-pack-1437.php</v>
       </c>
       <c r="L461" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/4-lom-zuckuss-2-pack-1437.jpg</v>
       </c>
       <c r="M461" t="str">
         <v/>
@@ -23534,7 +23534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/han-solo-carbonite-1436.php</v>
       </c>
       <c r="L462" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-carbonite-1436.jpg</v>
       </c>
       <c r="M462" t="str">
         <v/>
@@ -23584,7 +23584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/at-at-driver-1369.php</v>
       </c>
       <c r="L463" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/at-at-driver-1369.jpg</v>
       </c>
       <c r="M463" t="str">
         <v/>
@@ -23634,7 +23634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/boba-fett-esb-1461.php</v>
       </c>
       <c r="L464" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-esb-1461.jpg</v>
       </c>
       <c r="M464" t="str">
         <v/>
@@ -23684,7 +23684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/chewbacca-esb-1463.php</v>
       </c>
       <c r="L465" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/chewbacca-esb-1463.jpg</v>
       </c>
       <c r="M465" t="str">
         <v/>
@@ -23734,7 +23734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/darth-vader-esb-1465.php</v>
       </c>
       <c r="L466" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-esb-1465.jpg</v>
       </c>
       <c r="M466" t="str">
         <v/>
@@ -23784,7 +23784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/han-solo-bespin-1368.php</v>
       </c>
       <c r="L467" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-bespin-1368.jpg</v>
       </c>
       <c r="M467" t="str">
         <v/>
@@ -23834,7 +23834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/luke-skywalker-bespin-1371.php</v>
       </c>
       <c r="L468" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-bespin-1371.jpg</v>
       </c>
       <c r="M468" t="str">
         <v/>
@@ -23884,7 +23884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/luke-skywalker-dagobah-1462.php</v>
       </c>
       <c r="L469" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-dagobah-1462.jpg</v>
       </c>
       <c r="M469" t="str">
         <v/>
@@ -23934,7 +23934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/princess-leia-organa-hoth-1367.php</v>
       </c>
       <c r="L470" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/princess-leia-organa-hoth-1367.jpg</v>
       </c>
       <c r="M470" t="str">
         <v/>
@@ -23984,7 +23984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/imperial-snowtrooper-hoth-1464.php</v>
       </c>
       <c r="L471" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-snowtrooper-hoth-1464.jpg</v>
       </c>
       <c r="M471" t="str">
         <v/>
@@ -24034,7 +24034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/yoda-dagobah-1370.php</v>
       </c>
       <c r="L472" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/yoda-dagobah-1370.jpg</v>
       </c>
       <c r="M472" t="str">
         <v/>
@@ -24084,7 +24084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/lando-calrissian-1376.php</v>
       </c>
       <c r="L473" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/lando-calrissian-1376.jpg</v>
       </c>
       <c r="M473" t="str">
         <v/>
@@ -24134,7 +24134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/luke-skywalker-snowspeeder-1373.php</v>
       </c>
       <c r="L474" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-snowspeeder-1373.jpg</v>
       </c>
       <c r="M474" t="str">
         <v/>
@@ -24184,7 +24184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/r2-d2-esb-1372.php</v>
       </c>
       <c r="L475" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/r2-d2-esb-1372.jpg</v>
       </c>
       <c r="M475" t="str">
         <v/>
@@ -24234,7 +24234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/rebel-soldier-hoth-1375.php</v>
       </c>
       <c r="L476" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rebel-soldier-hoth-1375.jpg</v>
       </c>
       <c r="M476" t="str">
         <v/>
@@ -24284,7 +24284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/tie-fighter-pilot-esb-1374.php</v>
       </c>
       <c r="L477" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/tie-fighter-pilot-esb-1374.jpg</v>
       </c>
       <c r="M477" t="str">
         <v/>
@@ -24334,7 +24334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/admiral-ackbar-4826.php</v>
       </c>
       <c r="L478" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/admiral-ackbar-4826.jpg</v>
       </c>
       <c r="M478" t="str">
         <v/>
@@ -24384,7 +24384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/gamorrean-guard-5572.php</v>
       </c>
       <c r="L479" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/gamorrean-guard-5572.jpg</v>
       </c>
       <c r="M479" t="str">
         <v/>
@@ -24434,7 +24434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/anakin-skywalker-force-spirit-7120.php</v>
       </c>
       <c r="L480" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/anakin-skywalker-force-spirit-7120.jpg</v>
       </c>
       <c r="M480" t="str">
         <v/>
@@ -24484,7 +24484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/boba-fett-rotj-5453.php</v>
       </c>
       <c r="L481" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-rotj-5453.jpg</v>
       </c>
       <c r="M481" t="str">
         <v/>
@@ -24534,7 +24534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/force-ghosts-3-pack-6384.php</v>
       </c>
       <c r="L482" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/force-ghosts-3-pack-6384.jpg</v>
       </c>
       <c r="M482" t="str">
         <v/>
@@ -24584,7 +24584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/obi-wan-kenobi-force-spirit-7122.php</v>
       </c>
       <c r="L483" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-force-spirit-7122.jpg</v>
       </c>
       <c r="M483" t="str">
         <v/>
@@ -24634,7 +24634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/rebel-commando-endor-deluxe-6828.php</v>
       </c>
       <c r="L484" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rebel-commando-endor-deluxe-6828.jpg</v>
       </c>
       <c r="M484" t="str">
         <v/>
@@ -24684,7 +24684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/emperors-royal-guard-tie-pilot-carbonized-5527.php</v>
       </c>
       <c r="L485" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/emperors-royal-guard-tie-pilot-carbonized-5527.jpg</v>
       </c>
       <c r="M485" t="str">
         <v/>
@@ -24734,7 +24734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/yoda-force-spirit-7121.php</v>
       </c>
       <c r="L486" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/yoda-force-spirit-7121.jpg</v>
       </c>
       <c r="M486" t="str">
         <v/>
@@ -24784,7 +24784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/biker-scout-5271.php</v>
       </c>
       <c r="L487" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/biker-scout-5271.jpg</v>
       </c>
       <c r="M487" t="str">
         <v/>
@@ -24834,7 +24834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/han-solo-endor-5273.php</v>
       </c>
       <c r="L488" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-endor-5273.jpg</v>
       </c>
       <c r="M488" t="str">
         <v/>
@@ -24884,7 +24884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/lando-calrissian-skiff-guard-5272.php</v>
       </c>
       <c r="L489" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/lando-calrissian-skiff-guard-5272.jpg</v>
       </c>
       <c r="M489" t="str">
         <v/>
@@ -24934,7 +24934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/princess-leia-endor-5274.php</v>
       </c>
       <c r="L490" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/princess-leia-endor-5274.jpg</v>
       </c>
       <c r="M490" t="str">
         <v/>
@@ -24984,7 +24984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/wicket-5275.php</v>
       </c>
       <c r="L491" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/wicket-5275.jpg</v>
       </c>
       <c r="M491" t="str">
         <v/>
@@ -25034,7 +25034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/bib-fortuna-5541.php</v>
       </c>
       <c r="L492" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/bib-fortuna-5541.jpg</v>
       </c>
       <c r="M492" t="str">
         <v/>
@@ -25084,7 +25084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/chewbacca-rotj-5542.php</v>
       </c>
       <c r="L493" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/chewbacca-rotj-5542.jpg</v>
       </c>
       <c r="M493" t="str">
         <v/>
@@ -25134,7 +25134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/the-emperor-5543.php</v>
       </c>
       <c r="L494" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-emperor-5543.jpg</v>
       </c>
       <c r="M494" t="str">
         <v/>
@@ -25184,7 +25184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/paploo-5544.php</v>
       </c>
       <c r="L495" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/paploo-5544.jpg</v>
       </c>
       <c r="M495" t="str">
         <v/>
@@ -25234,7 +25234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/stormtrooper-rotj-5545.php</v>
       </c>
       <c r="L496" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/stormtrooper-rotj-5545.jpg</v>
       </c>
       <c r="M496" t="str">
         <v/>
@@ -25284,7 +25284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/darth-vader-rotj-6387.php</v>
       </c>
       <c r="L497" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-rotj-6387.jpg</v>
       </c>
       <c r="M497" t="str">
         <v/>
@@ -25334,7 +25334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/emperors-royal-guard-6388.php</v>
       </c>
       <c r="L498" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/emperors-royal-guard-6388.jpg</v>
       </c>
       <c r="M498" t="str">
         <v/>
@@ -25384,7 +25384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/luke-skywalker-jedi-knight-6386.php</v>
       </c>
       <c r="L499" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-jedi-knight-6386.jpg</v>
       </c>
       <c r="M499" t="str">
         <v/>
@@ -25434,7 +25434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/40th-anniversary/r2-d2-rotj-6385.php</v>
       </c>
       <c r="L500" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/r2-d2-rotj-6385.jpg</v>
       </c>
       <c r="M500" t="str">
         <v/>
@@ -25484,7 +25484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/anakin-skywalker-clone-wars-2378.php</v>
       </c>
       <c r="L501" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/anakin-skywalker-clone-wars-2378.jpg</v>
       </c>
       <c r="M501" t="str">
         <v/>
@@ -25534,7 +25534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/arc-trooper-echo-clone-wars-2381.php</v>
       </c>
       <c r="L502" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/arc-trooper-echo-clone-wars-2381.jpg</v>
       </c>
       <c r="M502" t="str">
         <v/>
@@ -25584,7 +25584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/battle-droid-tpm-1643.php</v>
       </c>
       <c r="L503" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/battle-droid-tpm-1643.jpg</v>
       </c>
       <c r="M503" t="str">
         <v/>
@@ -25634,7 +25634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/boba-fett-droids-3283.php</v>
       </c>
       <c r="L504" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-droids-3283.jpg</v>
       </c>
       <c r="M504" t="str">
         <v/>
@@ -25684,7 +25684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/clone-pilot-hawk-clone-wars-2380.php</v>
       </c>
       <c r="L505" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-pilot-hawk-clone-wars-2380.jpg</v>
       </c>
       <c r="M505" t="str">
         <v/>
@@ -25734,7 +25734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/greedo-kenner-1640.php</v>
       </c>
       <c r="L506" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/greedo-kenner-1640.jpg</v>
       </c>
       <c r="M506" t="str">
         <v/>
@@ -25784,7 +25784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/greedo-potf2-2719.php</v>
       </c>
       <c r="L507" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/greedo-potf2-2719.jpg</v>
       </c>
       <c r="M507" t="str">
         <v/>
@@ -25834,7 +25834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/han-solo-potf2-2718.php</v>
       </c>
       <c r="L508" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-potf2-2718.jpg</v>
       </c>
       <c r="M508" t="str">
         <v/>
@@ -25884,7 +25884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/jar-jar-binks-clone-wars-1644.php</v>
       </c>
       <c r="L509" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jar-jar-binks-clone-wars-1644.jpg</v>
       </c>
       <c r="M509" t="str">
         <v/>
@@ -25934,7 +25934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/jawa-kenner-1638.php</v>
       </c>
       <c r="L510" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jawa-kenner-1638.jpg</v>
       </c>
       <c r="M510" t="str">
         <v/>
@@ -25984,7 +25984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/obi-wan-kenobi-kenner-1639.php</v>
       </c>
       <c r="L511" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-kenner-1639.jpg</v>
       </c>
       <c r="M511" t="str">
         <v/>
@@ -26034,7 +26034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/luke-skywalker-potf2-2720.php</v>
       </c>
       <c r="L512" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-potf2-2720.jpg</v>
       </c>
       <c r="M512" t="str">
         <v/>
@@ -26084,7 +26084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/mace-windu-tpm-1641.php</v>
       </c>
       <c r="L513" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mace-windu-tpm-1641.jpg</v>
       </c>
       <c r="M513" t="str">
         <v/>
@@ -26134,7 +26134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/obi-wan-kenobi-clone-wars-2379.php</v>
       </c>
       <c r="L514" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-clone-wars-2379.jpg</v>
       </c>
       <c r="M514" t="str">
         <v/>
@@ -26184,7 +26184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/qui-gon-jinn-tpm-1642.php</v>
       </c>
       <c r="L515" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/qui-gon-jinn-tpm-1642.jpg</v>
       </c>
       <c r="M515" t="str">
         <v/>
@@ -26234,7 +26234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/carnor-jax-comic-2052.php</v>
       </c>
       <c r="L516" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/carnor-jax-comic-2052.jpg</v>
       </c>
       <c r="M516" t="str">
         <v/>
@@ -26284,7 +26284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/darth-maul-comic-2054.php</v>
       </c>
       <c r="L517" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-maul-comic-2054.jpg</v>
       </c>
       <c r="M517" t="str">
         <v/>
@@ -26334,7 +26334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/jaxxon-comic-2053.php</v>
       </c>
       <c r="L518" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jaxxon-comic-2053.jpg</v>
       </c>
       <c r="M518" t="str">
         <v/>
@@ -26384,7 +26384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/luke-skywalker-ysalamiri-comic-2051.php</v>
       </c>
       <c r="L519" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-ysalamiri-comic-2051.jpg</v>
       </c>
       <c r="M519" t="str">
         <v/>
@@ -26434,7 +26434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/arc-trooper-clone-wars-tartakovsky-2877.php</v>
       </c>
       <c r="L520" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/arc-trooper-clone-wars-tartakovsky-2877.jpg</v>
       </c>
       <c r="M520" t="str">
         <v/>
@@ -26484,7 +26484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/general-grievous-clone-wars-tartakovsky-2879.php</v>
       </c>
       <c r="L521" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/general-grievous-clone-wars-tartakovsky-2879.jpg</v>
       </c>
       <c r="M521" t="str">
         <v/>
@@ -26534,7 +26534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/george-lucas-stormtrooper-disguise-3334.php</v>
       </c>
       <c r="L522" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/george-lucas-stormtrooper-disguise-3334.jpg</v>
       </c>
       <c r="M522" t="str">
         <v/>
@@ -26584,7 +26584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/infinities-darth-vader-comic-4126.php</v>
       </c>
       <c r="L523" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/infinities-darth-vader-comic-4126.jpg</v>
       </c>
       <c r="M523" t="str">
         <v/>
@@ -26634,7 +26634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/princess-leia-organa-yavin-4-potf2-3647.php</v>
       </c>
       <c r="L524" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/princess-leia-organa-yavin-4-potf2-3647.jpg</v>
       </c>
       <c r="M524" t="str">
         <v/>
@@ -26684,7 +26684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/mace-windu-clone-wars-tartakovsky-2878.php</v>
       </c>
       <c r="L525" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mace-windu-clone-wars-tartakovsky-2878.jpg</v>
       </c>
       <c r="M525" t="str">
         <v/>
@@ -26734,7 +26734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/princess-leia-organa-comic-4127.php</v>
       </c>
       <c r="L526" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/princess-leia-organa-comic-4127.jpg</v>
       </c>
       <c r="M526" t="str">
         <v/>
@@ -26784,7 +26784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/sergeant-kreel-comic-4128.php</v>
       </c>
       <c r="L527" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sergeant-kreel-comic-4128.jpg</v>
       </c>
       <c r="M527" t="str">
         <v/>
@@ -26834,7 +26834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/black-krrsantan-comic-3990.php</v>
       </c>
       <c r="L528" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/black-krrsantan-comic-3990.jpg</v>
       </c>
       <c r="M528" t="str">
         <v/>
@@ -26884,7 +26884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/boba-fett-in-disguise-comic-4475.php</v>
       </c>
       <c r="L529" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-in-disguise-comic-4475.jpg</v>
       </c>
       <c r="M529" t="str">
         <v/>
@@ -26934,7 +26934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/doctor-aphra-comic-5506.php</v>
       </c>
       <c r="L530" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/doctor-aphra-comic-5506.jpg</v>
       </c>
       <c r="M530" t="str">
         <v/>
@@ -26984,7 +26984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/mara-jade-comic-5507.php</v>
       </c>
       <c r="L531" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mara-jade-comic-5507.jpg</v>
       </c>
       <c r="M531" t="str">
         <v/>
@@ -27034,7 +27034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/50th-anniversary/scar-trooper-mic-comic-5505.php</v>
       </c>
       <c r="L532" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/scar-trooper-mic-comic-5505.jpg</v>
       </c>
       <c r="M532" t="str">
         <v/>
@@ -27084,7 +27084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/boba-fett-and-han-carbonite-51.php</v>
       </c>
       <c r="L533" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-and-han-carbonite-51.jpg</v>
       </c>
       <c r="M533" t="str">
         <v/>
@@ -27134,7 +27134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/cantina-showdown-63.php</v>
       </c>
       <c r="L534" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cantina-showdown-63.jpg</v>
       </c>
       <c r="M534" t="str">
         <v/>
@@ -27184,7 +27184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/boba-fett-prototype-54.php</v>
       </c>
       <c r="L535" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-prototype-54.jpg</v>
       </c>
       <c r="M535" t="str">
         <v/>
@@ -27234,7 +27234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/jabba-hutt-sdcc-52.php</v>
       </c>
       <c r="L536" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jabba-hutt-sdcc-52.jpg</v>
       </c>
       <c r="M536" t="str">
         <v/>
@@ -27284,7 +27284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/walmart-mexico-4-pack-199.php</v>
       </c>
       <c r="L537" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/walmart-mexico-4-pack-199.jpg</v>
       </c>
       <c r="M537" t="str">
         <v/>
@@ -27334,7 +27334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/amazon-stormtrooper-4-pack-59.php</v>
       </c>
       <c r="L538" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/amazon-stormtrooper-4-pack-59.jpg</v>
       </c>
       <c r="M538" t="str">
         <v/>
@@ -27384,7 +27384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/battlefront-shock-trooper-58.php</v>
       </c>
       <c r="L539" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/battlefront-shock-trooper-58.jpg</v>
       </c>
       <c r="M539" t="str">
         <v/>
@@ -27434,7 +27434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/chewbacca-prototype-set-hasbro-employee-gift-7337.php</v>
       </c>
       <c r="L540" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/chewbacca-prototype-set-hasbro-employee-gift-7337.jpg</v>
       </c>
       <c r="M540" t="str">
         <v/>
@@ -27484,7 +27484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/darth-vader-emperors-wrath-57.php</v>
       </c>
       <c r="L541" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-emperors-wrath-57.jpg</v>
       </c>
       <c r="M541" t="str">
         <v/>
@@ -27534,7 +27534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/entertainment-earth-4-pack-60.php</v>
       </c>
       <c r="L542" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/entertainment-earth-4-pack-60.jpg</v>
       </c>
       <c r="M542" t="str">
         <v/>
@@ -27584,7 +27584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/first-order-stormtrooper-sdcc-53.php</v>
       </c>
       <c r="L543" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/first-order-stormtrooper-sdcc-53.jpg</v>
       </c>
       <c r="M543" t="str">
         <v/>
@@ -27634,7 +27634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/kylo-ren-starkiller-base-55.php</v>
       </c>
       <c r="L544" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kylo-ren-starkiller-base-55.jpg</v>
       </c>
       <c r="M544" t="str">
         <v/>
@@ -27684,7 +27684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/imperial-shadow-squadron-65.php</v>
       </c>
       <c r="L545" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-shadow-squadron-65.jpg</v>
       </c>
       <c r="M545" t="str">
         <v/>
@@ -27734,7 +27734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/snowtrooper-officer-56.php</v>
       </c>
       <c r="L546" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/snowtrooper-officer-56.jpg</v>
       </c>
       <c r="M546" t="str">
         <v/>
@@ -27784,7 +27784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/poe-dameron-riot-control-stormtrooper-68.php</v>
       </c>
       <c r="L547" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/poe-dameron-riot-control-stormtrooper-68.jpg</v>
       </c>
       <c r="M547" t="str">
         <v/>
@@ -27834,7 +27834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/c-3po-anh-195.php</v>
       </c>
       <c r="L548" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/c-3po-anh-195.jpg</v>
       </c>
       <c r="M548" t="str">
         <v/>
@@ -27884,7 +27884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/clone-troopers-ee-4-pack-196.php</v>
       </c>
       <c r="L549" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-troopers-ee-4-pack-196.jpg</v>
       </c>
       <c r="M549" t="str">
         <v/>
@@ -27934,7 +27934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/death-trooper-captain-cassian-jyn-erso-3-pack-193.php</v>
       </c>
       <c r="L550" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/death-trooper-captain-cassian-jyn-erso-3-pack-193.jpg</v>
       </c>
       <c r="M550" t="str">
         <v/>
@@ -27984,7 +27984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/droid-3-pack-140.php</v>
       </c>
       <c r="L551" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/droid-3-pack-140.jpg</v>
       </c>
       <c r="M551" t="str">
         <v/>
@@ -28034,7 +28034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/hovertank-pilot-157.php</v>
       </c>
       <c r="L552" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/hovertank-pilot-157.jpg</v>
       </c>
       <c r="M552" t="str">
         <v/>
@@ -28084,7 +28084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/jyn-erso-kmart-152.php</v>
       </c>
       <c r="L553" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jyn-erso-kmart-152.jpg</v>
       </c>
       <c r="M553" t="str">
         <v/>
@@ -28134,7 +28134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/jyn-erso-sdcc-144.php</v>
       </c>
       <c r="L554" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jyn-erso-sdcc-144.jpg</v>
       </c>
       <c r="M554" t="str">
         <v/>
@@ -28184,7 +28184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/kylo-ren-unmasked-sdcc-139.php</v>
       </c>
       <c r="L555" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kylo-ren-unmasked-sdcc-139.jpg</v>
       </c>
       <c r="M555" t="str">
         <v/>
@@ -28234,7 +28234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/obi-wan-kenobi-sdcc-138.php</v>
       </c>
       <c r="L556" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-sdcc-138.jpg</v>
       </c>
       <c r="M556" t="str">
         <v/>
@@ -28284,7 +28284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/rey-starkiller-base-61.php</v>
       </c>
       <c r="L557" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rey-starkiller-base-61.jpg</v>
       </c>
       <c r="M557" t="str">
         <v/>
@@ -28334,7 +28334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/scarif-stormtrooper-194.php</v>
       </c>
       <c r="L558" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/scarif-stormtrooper-194.jpg</v>
       </c>
       <c r="M558" t="str">
         <v/>
@@ -28384,7 +28384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/admiral-ackbar-and-first-order-officer-662.php</v>
       </c>
       <c r="L559" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/admiral-ackbar-and-first-order-officer-662.jpg</v>
       </c>
       <c r="M559" t="str">
         <v/>
@@ -28434,7 +28434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/imperial-at-act-driver-282.php</v>
       </c>
       <c r="L560" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-at-act-driver-282.jpg</v>
       </c>
       <c r="M560" t="str">
         <v/>
@@ -28484,7 +28484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/battlefront-ii-inferno-squadron-agent-347.php</v>
       </c>
       <c r="L561" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/battlefront-ii-inferno-squadron-agent-347.jpg</v>
       </c>
       <c r="M561" t="str">
         <v/>
@@ -28534,7 +28534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/clone-captain-rex-355.php</v>
       </c>
       <c r="L562" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-captain-rex-355.jpg</v>
       </c>
       <c r="M562" t="str">
         <v/>
@@ -28584,7 +28584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/commander-gree-343.php</v>
       </c>
       <c r="L563" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/commander-gree-343.jpg</v>
       </c>
       <c r="M563" t="str">
         <v/>
@@ -28634,7 +28634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/elite-praetorian-guard-heavy-blade-664.php</v>
       </c>
       <c r="L564" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/elite-praetorian-guard-heavy-blade-664.jpg</v>
       </c>
       <c r="M564" t="str">
         <v/>
@@ -28684,7 +28684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/first-order-stormtrooper-with-gear-663.php</v>
       </c>
       <c r="L565" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/first-order-stormtrooper-with-gear-663.jpg</v>
       </c>
       <c r="M565" t="str">
         <v/>
@@ -28734,7 +28734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/first-order-stormtrooper-executioner-655.php</v>
       </c>
       <c r="L566" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/first-order-stormtrooper-executioner-655.jpg</v>
       </c>
       <c r="M566" t="str">
         <v/>
@@ -28784,7 +28784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/guardians-of-evil-4-pack-658.php</v>
       </c>
       <c r="L567" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/guardians-of-evil-4-pack-658.jpg</v>
       </c>
       <c r="M567" t="str">
         <v/>
@@ -28834,7 +28834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/kylo-ren-in-throne-room-669.php</v>
       </c>
       <c r="L568" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kylo-ren-in-throne-room-669.jpg</v>
       </c>
       <c r="M568" t="str">
         <v/>
@@ -28884,7 +28884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/luke-skywalker-jedi-master-on-ahch-to-island-666.php</v>
       </c>
       <c r="L569" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-jedi-master-on-ahch-to-island-666.jpg</v>
       </c>
       <c r="M569" t="str">
         <v/>
@@ -28934,7 +28934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/luke-skywalker-and-rey-jedi-master-and-training-353.php</v>
       </c>
       <c r="L570" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-and-rey-jedi-master-and-training-353.jpg</v>
       </c>
       <c r="M570" t="str">
         <v/>
@@ -28984,7 +28984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/x-34-landspeeder-and-luke-skywalker-sdcc-342.php</v>
       </c>
       <c r="L571" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/x-34-landspeeder-and-luke-skywalker-sdcc-342.jpg</v>
       </c>
       <c r="M571" t="str">
         <v/>
@@ -29034,7 +29034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/obi-wan-kenobi-force-spirit-668.php</v>
       </c>
       <c r="L572" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-force-spirit-668.jpg</v>
       </c>
       <c r="M572" t="str">
         <v/>
@@ -29084,7 +29084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/rey-on-crait-667.php</v>
       </c>
       <c r="L573" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rey-on-crait-667.jpg</v>
       </c>
       <c r="M573" t="str">
         <v/>
@@ -29134,7 +29134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/supreme-leader-snoke-throne-665.php</v>
       </c>
       <c r="L574" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/supreme-leader-snoke-throne-665.jpg</v>
       </c>
       <c r="M574" t="str">
         <v/>
@@ -29184,7 +29184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/grand-admiral-thrawn-sdcc-346.php</v>
       </c>
       <c r="L575" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/grand-admiral-thrawn-sdcc-346.jpg</v>
       </c>
       <c r="M575" t="str">
         <v/>
@@ -29234,7 +29234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/admiral-piett-1049.php</v>
       </c>
       <c r="L576" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/admiral-piett-1049.jpg</v>
       </c>
       <c r="M576" t="str">
         <v/>
@@ -29284,7 +29284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/red-squadron-droid-3-pack-1019.php</v>
       </c>
       <c r="L577" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/red-squadron-droid-3-pack-1019.jpg</v>
       </c>
       <c r="M577" t="str">
         <v/>
@@ -29334,7 +29334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/captain-phasma-quicksilver-baton-1088.php</v>
       </c>
       <c r="L578" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/captain-phasma-quicksilver-baton-1088.jpg</v>
       </c>
       <c r="M578" t="str">
         <v/>
@@ -29384,7 +29384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/chewbacca-goggles-1042.php</v>
       </c>
       <c r="L579" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/chewbacca-goggles-1042.jpg</v>
       </c>
       <c r="M579" t="str">
         <v/>
@@ -29434,7 +29434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/commander-wolffe-1017.php</v>
       </c>
       <c r="L580" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/commander-wolffe-1017.jpg</v>
       </c>
       <c r="M580" t="str">
         <v/>
@@ -29484,7 +29484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/gamorrean-guard-deluxe-1010.php</v>
       </c>
       <c r="L581" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/gamorrean-guard-deluxe-1010.jpg</v>
       </c>
       <c r="M581" t="str">
         <v/>
@@ -29534,7 +29534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/general-veers-1057.php</v>
       </c>
       <c r="L582" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/general-veers-1057.jpg</v>
       </c>
       <c r="M582" t="str">
         <v/>
@@ -29584,7 +29584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/han-solo-and-princess-leia-organa-on-hoth-1115.php</v>
       </c>
       <c r="L583" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-and-princess-leia-organa-on-hoth-1115.jpg</v>
       </c>
       <c r="M583" t="str">
         <v/>
@@ -29634,7 +29634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/han-solo-mynock-1078.php</v>
       </c>
       <c r="L584" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-mynock-1078.jpg</v>
       </c>
       <c r="M584" t="str">
         <v/>
@@ -29684,7 +29684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/princess-leia-bespin-outfit-1056.php</v>
       </c>
       <c r="L585" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/princess-leia-bespin-outfit-1056.jpg</v>
       </c>
       <c r="M585" t="str">
         <v/>
@@ -29734,7 +29734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/mimban-stormtrooper-1020.php</v>
       </c>
       <c r="L586" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mimban-stormtrooper-1020.jpg</v>
       </c>
       <c r="M586" t="str">
         <v/>
@@ -29784,7 +29784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/moloch-chronos-1058.php</v>
       </c>
       <c r="L587" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/moloch-chronos-1058.jpg</v>
       </c>
       <c r="M587" t="str">
         <v/>
@@ -29834,7 +29834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/rey-kylo-starkiller-base-centerpiece-1079.php</v>
       </c>
       <c r="L588" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rey-kylo-starkiller-base-centerpiece-1079.jpg</v>
       </c>
       <c r="M588" t="str">
         <v/>
@@ -29884,7 +29884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/zuckuss-1018.php</v>
       </c>
       <c r="L589" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/zuckuss-1018.jpg</v>
       </c>
       <c r="M589" t="str">
         <v/>
@@ -29934,7 +29934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/c-3po-babu-frik-1325.php</v>
       </c>
       <c r="L590" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/c-3po-babu-frik-1325.jpg</v>
       </c>
       <c r="M590" t="str">
         <v/>
@@ -29984,7 +29984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/chewbacca-c-3po-1345.php</v>
       </c>
       <c r="L591" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/chewbacca-c-3po-1345.jpg</v>
       </c>
       <c r="M591" t="str">
         <v/>
@@ -30034,7 +30034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/clone-commander-fox-1319.php</v>
       </c>
       <c r="L592" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-commander-fox-1319.jpg</v>
       </c>
       <c r="M592" t="str">
         <v/>
@@ -30084,7 +30084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/clone-commander-obi-wan-kenobi-1247.php</v>
       </c>
       <c r="L593" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-commander-obi-wan-kenobi-1247.jpg</v>
       </c>
       <c r="M593" t="str">
         <v/>
@@ -30134,7 +30134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/darth-maul-duel-of-the-fates-1224.php</v>
       </c>
       <c r="L594" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-maul-duel-of-the-fates-1224.jpg</v>
       </c>
       <c r="M594" t="str">
         <v/>
@@ -30184,7 +30184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/emperor-palpatine-with-throne-1236.php</v>
       </c>
       <c r="L595" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/emperor-palpatine-with-throne-1236.jpg</v>
       </c>
       <c r="M595" t="str">
         <v/>
@@ -30234,7 +30234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/first-order-elite-snowtrooper-1315.php</v>
       </c>
       <c r="L596" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/first-order-elite-snowtrooper-1315.jpg</v>
       </c>
       <c r="M596" t="str">
         <v/>
@@ -30284,7 +30284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/ig-11-1326.php</v>
       </c>
       <c r="L597" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ig-11-1326.jpg</v>
       </c>
       <c r="M597" t="str">
         <v/>
@@ -30334,7 +30334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/imperial-jump-trooper-1181.php</v>
       </c>
       <c r="L598" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-jump-trooper-1181.jpg</v>
       </c>
       <c r="M598" t="str">
         <v/>
@@ -30384,7 +30384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/luke-skywalker-death-star-escape-1226.php</v>
       </c>
       <c r="L599" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-death-star-escape-1226.jpg</v>
       </c>
       <c r="M599" t="str">
         <v/>
@@ -30434,7 +30434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/luke-skywalker-skywalker-strikes-1317.php</v>
       </c>
       <c r="L600" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-skywalker-strikes-1317.jpg</v>
       </c>
       <c r="M600" t="str">
         <v/>
@@ -30484,7 +30484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/luke-skywalker-jedi-knight-1320.php</v>
       </c>
       <c r="L601" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-jedi-knight-1320.jpg</v>
       </c>
       <c r="M601" t="str">
         <v/>
@@ -30534,7 +30534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/obi-wan-duel-of-the-fates-1225.php</v>
       </c>
       <c r="L602" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-duel-of-the-fates-1225.jpg</v>
       </c>
       <c r="M602" t="str">
         <v/>
@@ -30584,7 +30584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/purge-stormtrooper-1314.php</v>
       </c>
       <c r="L603" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/purge-stormtrooper-1314.jpg</v>
       </c>
       <c r="M603" t="str">
         <v/>
@@ -30634,7 +30634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/red-sith-trooper-1277.php</v>
       </c>
       <c r="L604" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/red-sith-trooper-1277.jpg</v>
       </c>
       <c r="M604" t="str">
         <v/>
@@ -30684,7 +30684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/yoda-force-spirit-1346.php</v>
       </c>
       <c r="L605" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/yoda-force-spirit-1346.jpg</v>
       </c>
       <c r="M605" t="str">
         <v/>
@@ -30734,7 +30734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/cad-bane-todo-360-1523.php</v>
       </c>
       <c r="L606" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cad-bane-todo-360-1523.jpg</v>
       </c>
       <c r="M606" t="str">
         <v/>
@@ -30784,7 +30784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/heroes-of-endor-1535.php</v>
       </c>
       <c r="L607" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/heroes-of-endor-1535.jpg</v>
       </c>
       <c r="M607" t="str">
         <v/>
@@ -30834,7 +30834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/jango-fett-video-game-1472.php</v>
       </c>
       <c r="L608" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jango-fett-video-game-1472.jpg</v>
       </c>
       <c r="M608" t="str">
         <v/>
@@ -30884,7 +30884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/wampa-1534.php</v>
       </c>
       <c r="L609" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/wampa-1534.jpg</v>
       </c>
       <c r="M609" t="str">
         <v/>
@@ -30934,7 +30934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/trapper-wolf-2860.php</v>
       </c>
       <c r="L610" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/trapper-wolf-2860.jpg</v>
       </c>
       <c r="M610" t="str">
         <v/>
@@ -30984,7 +30984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/cantina-showdown-potf-2859.php</v>
       </c>
       <c r="L611" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cantina-showdown-potf-2859.jpg</v>
       </c>
       <c r="M611" t="str">
         <v/>
@@ -31034,7 +31034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/cassian-andor-and-b2emo-droid-4473.php</v>
       </c>
       <c r="L612" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cassian-andor-and-b2emo-droid-4473.jpg</v>
       </c>
       <c r="M612" t="str">
         <v/>
@@ -31084,7 +31084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/jawa-noris-force-5911.php</v>
       </c>
       <c r="L613" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jawa-noris-force-5911.jpg</v>
       </c>
       <c r="M613" t="str">
         <v/>
@@ -31134,7 +31134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/jon-favreau-paz-vizsla-4246.php</v>
       </c>
       <c r="L614" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jon-favreau-paz-vizsla-4246.jpg</v>
       </c>
       <c r="M614" t="str">
         <v/>
@@ -31184,7 +31184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/ahsoka-tano-hk-87-assassin-droid-2-pack-7227.php</v>
       </c>
       <c r="L615" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ahsoka-tano-hk-87-assassin-droid-2-pack-7227.jpg</v>
       </c>
       <c r="M615" t="str">
         <v/>
@@ -31234,7 +31234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/bo-katan-kryze-holocomm-collection-7330.php</v>
       </c>
       <c r="L616" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/bo-katan-kryze-holocomm-collection-7330.jpg</v>
       </c>
       <c r="M616" t="str">
         <v/>
@@ -31284,7 +31284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/cobb-vanth-cad-bane-6392.php</v>
       </c>
       <c r="L617" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cobb-vanth-cad-bane-6392.jpg</v>
       </c>
       <c r="M617" t="str">
         <v/>
@@ -31334,7 +31334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/obi-wan-kenobi-darth-vader-ralph-mcquarrie-4267.php</v>
       </c>
       <c r="L618" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-darth-vader-ralph-mcquarrie-4267.jpg</v>
       </c>
       <c r="M618" t="str">
         <v/>
@@ -31384,7 +31384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/rancor-2867.php</v>
       </c>
       <c r="L619" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rancor-2867.jpg</v>
       </c>
       <c r="M619" t="str">
         <v/>
@@ -31434,7 +31434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/reva-the-third-sister-force-fx-elite-lightsaber-4283.php</v>
       </c>
       <c r="L620" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/reva-the-third-sister-force-fx-elite-lightsaber-4283.jpg</v>
       </c>
       <c r="M620" t="str">
         <v/>
@@ -31484,7 +31484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/starkiller-troopers-set-force-unleashed-6898.php</v>
       </c>
       <c r="L621" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/starkiller-troopers-set-force-unleashed-6898.jpg</v>
       </c>
       <c r="M621" t="str">
         <v/>
@@ -31534,7 +31534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/ahsoka-tano-holocomm-collection-7331.php</v>
       </c>
       <c r="L622" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ahsoka-tano-holocomm-collection-7331.jpg</v>
       </c>
       <c r="M622" t="str">
         <v/>
@@ -31584,7 +31584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/axe-woves-holocomm-collection-7309.php</v>
       </c>
       <c r="L623" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/axe-woves-holocomm-collection-7309.jpg</v>
       </c>
       <c r="M623" t="str">
         <v/>
@@ -31634,7 +31634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/c-3po-b1-battle-droid-body-super-battle-droid-2-pack-7934.php</v>
       </c>
       <c r="L624" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/c-3po-b1-battle-droid-body-super-battle-droid-2-pack-7934.jpg</v>
       </c>
       <c r="M624" t="str">
         <v/>
@@ -31684,7 +31684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/captain-enoch-night-trooper-8520.php</v>
       </c>
       <c r="L625" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/captain-enoch-night-trooper-8520.jpg</v>
       </c>
       <c r="M625" t="str">
         <v/>
@@ -31734,7 +31734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/darth-maul-holocomm-collection-8346.php</v>
       </c>
       <c r="L626" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-maul-holocomm-collection-8346.jpg</v>
       </c>
       <c r="M626" t="str">
         <v/>
@@ -31784,7 +31784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/darth-vader-holocomm-collection-8397.php</v>
       </c>
       <c r="L627" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-holocomm-collection-8397.jpg</v>
       </c>
       <c r="M627" t="str">
         <v/>
@@ -31834,7 +31834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/ezra-bridger-holocomm-collection-8592.php</v>
       </c>
       <c r="L628" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ezra-bridger-holocomm-collection-8592.jpg</v>
       </c>
       <c r="M628" t="str">
         <v/>
@@ -31884,7 +31884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/fallen-order-3-pack-cal-kestis-purge-trooper-second-sister-8126.php</v>
       </c>
       <c r="L629" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/fallen-order-3-pack-cal-kestis-purge-trooper-second-sister-8126.jpg</v>
       </c>
       <c r="M629" t="str">
         <v/>
@@ -31934,7 +31934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/han-solo-holocomm-collection-7328.php</v>
       </c>
       <c r="L630" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-holocomm-collection-7328.jpg</v>
       </c>
       <c r="M630" t="str">
         <v/>
@@ -31984,7 +31984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/the-last-command-4-pack-8413.php</v>
       </c>
       <c r="L631" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-last-command-4-pack-8413.jpg</v>
       </c>
       <c r="M631" t="str">
         <v/>
@@ -32034,7 +32034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/mae-assassin-holocomm-collection-8756.php</v>
       </c>
       <c r="L632" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mae-assassin-holocomm-collection-8756.jpg</v>
       </c>
       <c r="M632" t="str">
         <v/>
@@ -32084,7 +32084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/magnaguard-super-battle-droid-and-battle-droid-set-8529.php</v>
       </c>
       <c r="L633" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/magnaguard-super-battle-droid-and-battle-droid-set-8529.jpg</v>
       </c>
       <c r="M633" t="str">
         <v/>
@@ -32134,7 +32134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/masters-of-evil-3-pack-8348.php</v>
       </c>
       <c r="L634" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/masters-of-evil-3-pack-8348.jpg</v>
       </c>
       <c r="M634" t="str">
         <v/>
@@ -32184,7 +32184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/osha-aniseya-holocomm-collection-8593.php</v>
       </c>
       <c r="L635" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/osha-aniseya-holocomm-collection-8593.jpg</v>
       </c>
       <c r="M635" t="str">
         <v/>
@@ -32234,7 +32234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/phase-i-clone-trooper-lieutenant-332nd-ahsokas-clone-trooper-7685.php</v>
       </c>
       <c r="L636" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/phase-i-clone-trooper-lieutenant-332nd-ahsokas-clone-trooper-7685.jpg</v>
       </c>
       <c r="M636" t="str">
         <v/>
@@ -32284,7 +32284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/phase-ii-clone-trooper-battle-droid-8412.php</v>
       </c>
       <c r="L637" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/phase-ii-clone-trooper-battle-droid-8412.jpg</v>
       </c>
       <c r="M637" t="str">
         <v/>
@@ -32334,7 +32334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/qui-gon-jinn-obi-wan-kenobi-darth-maul-action-figure-set-8524.php</v>
       </c>
       <c r="L638" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/qui-gon-jinn-obi-wan-kenobi-darth-maul-action-figure-set-8524.jpg</v>
       </c>
       <c r="M638" t="str">
         <v/>
@@ -32384,7 +32384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/r5-d4-bd-72-and-pit-droids-8484.php</v>
       </c>
       <c r="L639" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/r5-d4-bd-72-and-pit-droids-8484.jpg</v>
       </c>
       <c r="M639" t="str">
         <v/>
@@ -32434,7 +32434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/rebel-trooper-stormtrooper-8803.php</v>
       </c>
       <c r="L640" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rebel-trooper-stormtrooper-8803.jpg</v>
       </c>
       <c r="M640" t="str">
         <v/>
@@ -32484,7 +32484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/shriek-hawk-trainers-8755.php</v>
       </c>
       <c r="L641" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/shriek-hawk-trainers-8755.jpg</v>
       </c>
       <c r="M641" t="str">
         <v/>
@@ -32534,7 +32534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/stap-battle-droid-8854.php</v>
       </c>
       <c r="L642" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/stap-battle-droid-8854.jpg</v>
       </c>
       <c r="M642" t="str">
         <v/>
@@ -32584,7 +32584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/the-mandalorian-holocomm-collection-7329.php</v>
       </c>
       <c r="L643" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-mandalorian-holocomm-collection-7329.jpg</v>
       </c>
       <c r="M643" t="str">
         <v/>
@@ -32634,7 +32634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/aayla-secura-revenge-of-the-sith-10745.php</v>
       </c>
       <c r="L644" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/aayla-secura-revenge-of-the-sith-10745.jpg</v>
       </c>
       <c r="M644" t="str">
         <v/>
@@ -32684,7 +32684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/anakin-skywalker-obi-wan-kenobi-mustafar-duel-11444.php</v>
       </c>
       <c r="L645" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/anakin-skywalker-obi-wan-kenobi-mustafar-duel-11444.jpg</v>
       </c>
       <c r="M645" t="str">
         <v/>
@@ -32734,7 +32734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/anakin-skywalker-clone-captain-rex-11420.php</v>
       </c>
       <c r="L646" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/anakin-skywalker-clone-captain-rex-11420.jpg</v>
       </c>
       <c r="M646" t="str">
         <v/>
@@ -32784,7 +32784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/cal-kestis-bd-1-turgle-skoova-stev-multipack-10626.php</v>
       </c>
       <c r="L647" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/cal-kestis-bd-1-turgle-skoova-stev-multipack-10626.jpg</v>
       </c>
       <c r="M647" t="str">
         <v/>
@@ -32834,7 +32834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/commander-cody-20th-anniversary-9032.php</v>
       </c>
       <c r="L648" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/commander-cody-20th-anniversary-9032.jpg</v>
       </c>
       <c r="M648" t="str">
         <v/>
@@ -32884,7 +32884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/count-dooku-revenge-of-the-sith-10363.php</v>
       </c>
       <c r="L649" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/count-dooku-revenge-of-the-sith-10363.jpg</v>
       </c>
       <c r="M649" t="str">
         <v/>
@@ -32934,7 +32934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/darth-vader-luke-skywalker-11419.php</v>
       </c>
       <c r="L650" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-luke-skywalker-11419.jpg</v>
       </c>
       <c r="M650" t="str">
         <v/>
@@ -32984,7 +32984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/kit-fisto-revenge-of-the-sith-10360.php</v>
       </c>
       <c r="L651" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kit-fisto-revenge-of-the-sith-10360.jpg</v>
       </c>
       <c r="M651" t="str">
         <v/>
@@ -33034,7 +33034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/kx-security-droid-enforcer-droideka-10768.php</v>
       </c>
       <c r="L652" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kx-security-droid-enforcer-droideka-10768.jpg</v>
       </c>
       <c r="M652" t="str">
         <v/>
@@ -33084,7 +33084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/luke-skywalker-imperial-guard-princess-leia-organa-boushh-2-pack-9085.php</v>
       </c>
       <c r="L653" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-imperial-guard-princess-leia-organa-boushh-2-pack-9085.jpg</v>
       </c>
       <c r="M653" t="str">
         <v/>
@@ -33134,7 +33134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/mace-windu-darth-sidious-12184.php</v>
       </c>
       <c r="L654" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mace-windu-darth-sidious-12184.jpg</v>
       </c>
       <c r="M654" t="str">
         <v/>
@@ -33184,7 +33184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/magnaguard-revenge-of-the-sith-10746.php</v>
       </c>
       <c r="L655" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/magnaguard-revenge-of-the-sith-10746.jpg</v>
       </c>
       <c r="M655" t="str">
         <v/>
@@ -33234,7 +33234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/obi-wan-kenobi-clone-trooper-212th-9152.php</v>
       </c>
       <c r="L656" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-clone-trooper-212th-9152.jpg</v>
       </c>
       <c r="M656" t="str">
         <v/>
@@ -33284,7 +33284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/phase-i-clone-trooper-super-battle-droid-9087.php</v>
       </c>
       <c r="L657" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/phase-i-clone-trooper-super-battle-droid-9087.jpg</v>
       </c>
       <c r="M657" t="str">
         <v/>
@@ -33334,7 +33334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/r2-d2-revenge-of-the-sith-10364.php</v>
       </c>
       <c r="L658" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/r2-d2-revenge-of-the-sith-10364.jpg</v>
       </c>
       <c r="M658" t="str">
         <v/>
@@ -33384,7 +33384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/shoretrooper-death-trooper-10758.php</v>
       </c>
       <c r="L659" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/shoretrooper-death-trooper-10758.jpg</v>
       </c>
       <c r="M659" t="str">
         <v/>
@@ -33434,7 +33434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/tactical-ops-trooper-revenge-of-the-sith-10361.php</v>
       </c>
       <c r="L660" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/tactical-ops-trooper-revenge-of-the-sith-10361.jpg</v>
       </c>
       <c r="M660" t="str">
         <v/>
@@ -33484,7 +33484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/the-ronin-r5-d56-visions-10625.php</v>
       </c>
       <c r="L661" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-ronin-r5-d56-visions-10625.jpg</v>
       </c>
       <c r="M661" t="str">
         <v/>
@@ -33534,7 +33534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/arc-trooper-infiltrator-commando-droid-training-12643.php</v>
       </c>
       <c r="L662" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/arc-trooper-infiltrator-commando-droid-training-12643.jpg</v>
       </c>
       <c r="M662" t="str">
         <v/>
@@ -33584,7 +33584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/darth-nihilus-darth-traya-knights-of-the-old-republic-ii-13489.php</v>
       </c>
       <c r="L663" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-nihilus-darth-traya-knights-of-the-old-republic-ii-13489.jpg</v>
       </c>
       <c r="M663" t="str">
         <v/>
@@ -33634,7 +33634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/misty-cav-scar-squadron-12922.php</v>
       </c>
       <c r="L664" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/misty-cav-scar-squadron-12922.jpg</v>
       </c>
       <c r="M664" t="str">
         <v/>
@@ -33684,7 +33684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/phase-i-assault-trooper-battle-droid-officer-12489.php</v>
       </c>
       <c r="L665" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/phase-i-assault-trooper-battle-droid-officer-12489.jpg</v>
       </c>
       <c r="M665" t="str">
         <v/>
@@ -33734,7 +33734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/exclusives/plo-koon-clone-commander-wolffe-13039.php</v>
       </c>
       <c r="L666" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/plo-koon-clone-commander-wolffe-13039.jpg</v>
       </c>
       <c r="M666" t="str">
         <v/>
@@ -33784,7 +33784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/carbonized/first-order-jet-trooper-carbonized-1310.php</v>
       </c>
       <c r="L667" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/first-order-jet-trooper-carbonized-1310.jpg</v>
       </c>
       <c r="M667" t="str">
         <v/>
@@ -33834,7 +33834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/carbonized/the-mandalorian-carbonized-1309.php</v>
       </c>
       <c r="L668" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-mandalorian-carbonized-1309.jpg</v>
       </c>
       <c r="M668" t="str">
         <v/>
@@ -33884,7 +33884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/carbonized/second-sister-inquisitor-carbonized-1311.php</v>
       </c>
       <c r="L669" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/second-sister-inquisitor-carbonized-1311.jpg</v>
       </c>
       <c r="M669" t="str">
         <v/>
@@ -33934,7 +33934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/carbonized/sith-trooper-carbonized-1308.php</v>
       </c>
       <c r="L670" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sith-trooper-carbonized-1308.jpg</v>
       </c>
       <c r="M670" t="str">
         <v/>
@@ -33984,7 +33984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/carbonized/boba-fett-carbonized-1414.php</v>
       </c>
       <c r="L671" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-carbonized-1414.jpg</v>
       </c>
       <c r="M671" t="str">
         <v/>
@@ -34034,7 +34034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/carbonized/darth-vader-carbonized-1435.php</v>
       </c>
       <c r="L672" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-carbonized-1435.jpg</v>
       </c>
       <c r="M672" t="str">
         <v/>
@@ -34084,7 +34084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/carbonized/stormtrooper-carbonized-1413.php</v>
       </c>
       <c r="L673" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/stormtrooper-carbonized-1413.jpg</v>
       </c>
       <c r="M673" t="str">
         <v/>
@@ -34134,7 +34134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/carbonized/ned-b-purge-trooper-carbonized-5930.php</v>
       </c>
       <c r="L674" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ned-b-purge-trooper-carbonized-5930.jpg</v>
       </c>
       <c r="M674" t="str">
         <v/>
@@ -34184,7 +34184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxys-edge/galaxy-edge-first-order-kylo-ren-1274.php</v>
       </c>
       <c r="L675" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/galaxy-edge-first-order-kylo-ren-1274.jpg</v>
       </c>
       <c r="M675" t="str">
         <v/>
@@ -34234,7 +34234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxys-edge/galaxy-edge-smugglers-run-1275.php</v>
       </c>
       <c r="L676" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/galaxy-edge-smugglers-run-1275.jpg</v>
       </c>
       <c r="M676" t="str">
         <v/>
@@ -34284,7 +34284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxys-edge/galaxy-edge-droid-depot-1276.php</v>
       </c>
       <c r="L677" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/galaxy-edge-droid-depot-1276.jpg</v>
       </c>
       <c r="M677" t="str">
         <v/>
@@ -34334,7 +34334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxys-edge/captain-cardinal-1525.php</v>
       </c>
       <c r="L678" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/captain-cardinal-1525.jpg</v>
       </c>
       <c r="M678" t="str">
         <v/>
@@ -34384,7 +34384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxys-edge/commander-pyre-1577.php</v>
       </c>
       <c r="L679" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/commander-pyre-1577.jpg</v>
       </c>
       <c r="M679" t="str">
         <v/>
@@ -34434,7 +34434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxys-edge/dj-r-3x-1524.php</v>
       </c>
       <c r="L680" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/dj-r-3x-1524.jpg</v>
       </c>
       <c r="M680" t="str">
         <v/>
@@ -34484,7 +34484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxys-edge/hondo-ohnaka-1510.php</v>
       </c>
       <c r="L681" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/hondo-ohnaka-1510.jpg</v>
       </c>
       <c r="M681" t="str">
         <v/>
@@ -34534,7 +34534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxys-edge/mountain-trooper-1729.php</v>
       </c>
       <c r="L682" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mountain-trooper-1729.jpg</v>
       </c>
       <c r="M682" t="str">
         <v/>
@@ -34584,7 +34584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxys-edge/r5-p8-1578.php</v>
       </c>
       <c r="L683" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/r5-p8-1578.jpg</v>
       </c>
       <c r="M683" t="str">
         <v/>
@@ -34634,7 +34634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxys-edge/galaxy-edge-droid-depot-k-7r1cb-23-pit-droid-and-babu-frik-3543.php</v>
       </c>
       <c r="L684" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/galaxy-edge-droid-depot-k-7r1cb-23-pit-droid-and-babu-frik-3543.jpg</v>
       </c>
       <c r="M684" t="str">
         <v/>
@@ -34684,7 +34684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxys-edge/galaxy-edge-first-order-general-hux-3542.php</v>
       </c>
       <c r="L685" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/galaxy-edge-first-order-general-hux-3542.jpg</v>
       </c>
       <c r="M685" t="str">
         <v/>
@@ -34734,7 +34734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxys-edge/galaxy-edge-galactic-creatures-3541.php</v>
       </c>
       <c r="L686" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/galaxy-edge-galactic-creatures-3541.jpg</v>
       </c>
       <c r="M686" t="str">
         <v/>
@@ -34784,7 +34784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/galaxys-edge/dok-ondar-6649.php</v>
       </c>
       <c r="L687" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/dok-ondar-6649.jpg</v>
       </c>
       <c r="M687" t="str">
         <v/>
@@ -34834,7 +34834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/gaming-greats/heavy-battle-droid-battlefront-ii-1348.php</v>
       </c>
       <c r="L688" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/heavy-battle-droid-battlefront-ii-1348.jpg</v>
       </c>
       <c r="M688" t="str">
         <v/>
@@ -34884,7 +34884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/gaming-greats/jedi-knight-revan-galaxy-heroes-1347.php</v>
       </c>
       <c r="L689" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jedi-knight-revan-galaxy-heroes-1347.jpg</v>
       </c>
       <c r="M689" t="str">
         <v/>
@@ -34934,7 +34934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/gaming-greats/darth-nihilus-kotr-ii-1528.php</v>
       </c>
       <c r="L690" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-nihilus-kotr-ii-1528.jpg</v>
       </c>
       <c r="M690" t="str">
         <v/>
@@ -34984,7 +34984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/gaming-greats/electrostaff-purge-trooper-fallen-order-1511.php</v>
       </c>
       <c r="L691" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/electrostaff-purge-trooper-fallen-order-1511.jpg</v>
       </c>
       <c r="M691" t="str">
         <v/>
@@ -35034,7 +35034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/gaming-greats/scout-trooper-fallen-order-1575.php</v>
       </c>
       <c r="L692" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/scout-trooper-fallen-order-1575.jpg</v>
       </c>
       <c r="M692" t="str">
         <v/>
@@ -35084,7 +35084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/gaming-greats/shadow-stormtrooper-force-unleashed-1438.php</v>
       </c>
       <c r="L693" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/shadow-stormtrooper-force-unleashed-1438.jpg</v>
       </c>
       <c r="M693" t="str">
         <v/>
@@ -35134,7 +35134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/gaming-greats/stormtrooper-commander-force-unleashed-1408.php</v>
       </c>
       <c r="L694" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/stormtrooper-commander-force-unleashed-1408.jpg</v>
       </c>
       <c r="M694" t="str">
         <v/>
@@ -35184,7 +35184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/clone-trooper-holiday-1563.php</v>
       </c>
       <c r="L695" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-trooper-holiday-1563.jpg</v>
       </c>
       <c r="M695" t="str">
         <v/>
@@ -35234,7 +35234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/range-trooper-holiday-1562.php</v>
       </c>
       <c r="L696" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/range-trooper-holiday-1562.jpg</v>
       </c>
       <c r="M696" t="str">
         <v/>
@@ -35284,7 +35284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/sith-trooper-holiday-1549.php</v>
       </c>
       <c r="L697" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sith-trooper-holiday-1549.jpg</v>
       </c>
       <c r="M697" t="str">
         <v/>
@@ -35334,7 +35334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/snowtrooper-and-porg-holiday-1541.php</v>
       </c>
       <c r="L698" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/snowtrooper-and-porg-holiday-1541.jpg</v>
       </c>
       <c r="M698" t="str">
         <v/>
@@ -35384,7 +35384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/stormtrooper-and-porg-holiday-1542.php</v>
       </c>
       <c r="L699" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/stormtrooper-and-porg-holiday-1542.jpg</v>
       </c>
       <c r="M699" t="str">
         <v/>
@@ -35434,7 +35434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/clone-trooper-halloween-edition-5234.php</v>
       </c>
       <c r="L700" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-trooper-halloween-edition-5234.jpg</v>
       </c>
       <c r="M700" t="str">
         <v/>
@@ -35484,7 +35484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/phase-ii-clone-trooper-holiday-5243.php</v>
       </c>
       <c r="L701" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/phase-ii-clone-trooper-holiday-5243.jpg</v>
       </c>
       <c r="M701" t="str">
         <v/>
@@ -35534,7 +35534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/first-order-stormtrooper-holiday-5066.php</v>
       </c>
       <c r="L702" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/first-order-stormtrooper-holiday-5066.jpg</v>
       </c>
       <c r="M702" t="str">
         <v/>
@@ -35584,7 +35584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/mandalorian-warrior-holiday-5065.php</v>
       </c>
       <c r="L703" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mandalorian-warrior-holiday-5065.jpg</v>
       </c>
       <c r="M703" t="str">
         <v/>
@@ -35634,7 +35634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/protocol-droid-holiday-edition-5244.php</v>
       </c>
       <c r="L704" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/protocol-droid-holiday-edition-5244.jpg</v>
       </c>
       <c r="M704" t="str">
         <v/>
@@ -35684,7 +35684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/scout-trooper-holiday-5064.php</v>
       </c>
       <c r="L705" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/scout-trooper-holiday-5064.jpg</v>
       </c>
       <c r="M705" t="str">
         <v/>
@@ -35734,7 +35734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/wookiee-halloween-edition-5235.php</v>
       </c>
       <c r="L706" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/wookiee-halloween-edition-5235.jpg</v>
       </c>
       <c r="M706" t="str">
         <v/>
@@ -35784,7 +35784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/wookiee-holiday-5063.php</v>
       </c>
       <c r="L707" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/wookiee-holiday-5063.jpg</v>
       </c>
       <c r="M707" t="str">
         <v/>
@@ -35834,7 +35834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/ewok-holiday-7229.php</v>
       </c>
       <c r="L708" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ewok-holiday-7229.jpg</v>
       </c>
       <c r="M708" t="str">
         <v/>
@@ -35884,7 +35884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/jawa-salacious-b-crumb-holiday-7228.php</v>
       </c>
       <c r="L709" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jawa-salacious-b-crumb-holiday-7228.jpg</v>
       </c>
       <c r="M709" t="str">
         <v/>
@@ -35934,7 +35934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/mandalorian-scout-holiday-7226.php</v>
       </c>
       <c r="L710" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mandalorian-scout-holiday-7226.jpg</v>
       </c>
       <c r="M710" t="str">
         <v/>
@@ -35984,7 +35984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/purge-trooper-holiday-7230.php</v>
       </c>
       <c r="L711" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/purge-trooper-holiday-7230.jpg</v>
       </c>
       <c r="M711" t="str">
         <v/>
@@ -36034,7 +36034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/snowtrooper-holiday-7236.php</v>
       </c>
       <c r="L712" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/snowtrooper-holiday-7236.jpg</v>
       </c>
       <c r="M712" t="str">
         <v/>
@@ -36084,7 +36084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/inquisitor-duros-bounty-hunter-halloween-edition-8691.php</v>
       </c>
       <c r="L713" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/inquisitor-duros-bounty-hunter-halloween-edition-8691.jpg</v>
       </c>
       <c r="M713" t="str">
         <v/>
@@ -36134,7 +36134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/kx-security-droid-holiday-7332.php</v>
       </c>
       <c r="L714" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kx-security-droid-holiday-7332.jpg</v>
       </c>
       <c r="M714" t="str">
         <v/>
@@ -36184,7 +36184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/astromech-droid-holiday-11881.php</v>
       </c>
       <c r="L715" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/astromech-droid-holiday-11881.jpg</v>
       </c>
       <c r="M715" t="str">
         <v/>
@@ -36234,7 +36234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/dathomir-witch-halloween-edition-11872.php</v>
       </c>
       <c r="L716" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/dathomir-witch-halloween-edition-11872.jpg</v>
       </c>
       <c r="M716" t="str">
         <v/>
@@ -36284,7 +36284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/night-trooper-halloween-edition-11373.php</v>
       </c>
       <c r="L717" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/night-trooper-halloween-edition-11373.jpg</v>
       </c>
       <c r="M717" t="str">
         <v/>
@@ -36334,7 +36334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/imperial-royal-guard-halloween-edition-11556.php</v>
       </c>
       <c r="L718" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-royal-guard-halloween-edition-11556.jpg</v>
       </c>
       <c r="M718" t="str">
         <v/>
@@ -36384,7 +36384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/stormtrooper-holiday-11882.php</v>
       </c>
       <c r="L719" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/stormtrooper-holiday-11882.jpg</v>
       </c>
       <c r="M719" t="str">
         <v/>
@@ -36434,7 +36434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/holiday/ewok-valentines-day-edition-12355.php</v>
       </c>
       <c r="L720" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ewok-valentines-day-edition-12355.jpg</v>
       </c>
       <c r="M720" t="str">
         <v/>
@@ -36484,7 +36484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/speeder-bike-and-biker-scout-62.php</v>
       </c>
       <c r="L721" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/speeder-bike-and-biker-scout-62.jpg</v>
       </c>
       <c r="M721" t="str">
         <v/>
@@ -36534,7 +36534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/jabba-the-hutt-64.php</v>
       </c>
       <c r="L722" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jabba-the-hutt-64.jpg</v>
       </c>
       <c r="M722" t="str">
         <v/>
@@ -36584,7 +36584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/han-solo-and-tauntaun-67.php</v>
       </c>
       <c r="L723" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/han-solo-and-tauntaun-67.jpg</v>
       </c>
       <c r="M723" t="str">
         <v/>
@@ -36634,7 +36634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/luke-skywalker-wampa-66.php</v>
       </c>
       <c r="L724" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-wampa-66.jpg</v>
       </c>
       <c r="M724" t="str">
         <v/>
@@ -36684,7 +36684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/porgs-2-pack-1040.php</v>
       </c>
       <c r="L725" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/porgs-2-pack-1040.jpg</v>
       </c>
       <c r="M725" t="str">
         <v/>
@@ -36734,7 +36734,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/stormtrooper-with-blast-accessories-1052.php</v>
       </c>
       <c r="L726" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/stormtrooper-with-blast-accessories-1052.jpg</v>
       </c>
       <c r="M726" t="str">
         <v/>
@@ -36784,7 +36784,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/the-child-the-mandalorian-1416.php</v>
       </c>
       <c r="L727" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-child-the-mandalorian-1416.jpg</v>
       </c>
       <c r="M727" t="str">
         <v/>
@@ -36834,7 +36834,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/snowspeeder-1366.php</v>
       </c>
       <c r="L728" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/snowspeeder-1366.jpg</v>
       </c>
       <c r="M728" t="str">
         <v/>
@@ -36884,7 +36884,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/darth-vader-revenge-of-the-jedi-6390.php</v>
       </c>
       <c r="L729" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-revenge-of-the-jedi-6390.jpg</v>
       </c>
       <c r="M729" t="str">
         <v/>
@@ -36934,7 +36934,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/jabba-the-hutt-salacious-b-crumb-rotj-6389.php</v>
       </c>
       <c r="L730" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/jabba-the-hutt-salacious-b-crumb-rotj-6389.jpg</v>
       </c>
       <c r="M730" t="str">
         <v/>
@@ -36984,7 +36984,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/darth-maul-sith-speeder-8808.php</v>
       </c>
       <c r="L731" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-maul-sith-speeder-8808.jpg</v>
       </c>
       <c r="M731" t="str">
         <v/>
@@ -37034,7 +37034,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/emperor-palpatine-throne-reissue-8528.php</v>
       </c>
       <c r="L732" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/emperor-palpatine-throne-reissue-8528.jpg</v>
       </c>
       <c r="M732" t="str">
         <v/>
@@ -37084,7 +37084,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/tie-fighter-69.php</v>
       </c>
       <c r="L733" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/tie-fighter-69.jpg</v>
       </c>
       <c r="M733" t="str">
         <v/>
@@ -37134,7 +37134,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/x-34-landspeeder-and-luke-skywalker-645.php</v>
       </c>
       <c r="L734" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/x-34-landspeeder-and-luke-skywalker-645.jpg</v>
       </c>
       <c r="M734" t="str">
         <v/>
@@ -37184,7 +37184,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/scavenger-rey-and-speeder-341.php</v>
       </c>
       <c r="L735" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/scavenger-rey-and-speeder-341.jpg</v>
       </c>
       <c r="M735" t="str">
         <v/>
@@ -37234,7 +37234,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/sandtrooper-and-dewback-357.php</v>
       </c>
       <c r="L736" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sandtrooper-and-dewback-357.jpg</v>
       </c>
       <c r="M736" t="str">
         <v/>
@@ -37284,7 +37284,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/enfys-nest-swoop-bike-1053.php</v>
       </c>
       <c r="L737" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/enfys-nest-swoop-bike-1053.jpg</v>
       </c>
       <c r="M737" t="str">
         <v/>
@@ -37334,7 +37334,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/darth-vader-centerpiece-644.php</v>
       </c>
       <c r="L738" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-centerpiece-644.jpg</v>
       </c>
       <c r="M738" t="str">
         <v/>
@@ -37384,7 +37384,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/luke-skywalker-centerpiece-643.php</v>
       </c>
       <c r="L739" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-centerpiece-643.jpg</v>
       </c>
       <c r="M739" t="str">
         <v/>
@@ -37434,7 +37434,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/kylo-ren-centerpiece-1021.php</v>
       </c>
       <c r="L740" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kylo-ren-centerpiece-1021.jpg</v>
       </c>
       <c r="M740" t="str">
         <v/>
@@ -37484,7 +37484,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/rey-starkiller-base-centerpiece-1139.php</v>
       </c>
       <c r="L741" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rey-starkiller-base-centerpiece-1139.jpg</v>
       </c>
       <c r="M741" t="str">
         <v/>
@@ -37534,7 +37534,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/general-grievous-1137.php</v>
       </c>
       <c r="L742" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/general-grievous-1137.jpg</v>
       </c>
       <c r="M742" t="str">
         <v/>
@@ -37584,7 +37584,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/heavy-infantry-mandalorian-1349.php</v>
       </c>
       <c r="L743" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/heavy-infantry-mandalorian-1349.jpg</v>
       </c>
       <c r="M743" t="str">
         <v/>
@@ -37634,7 +37634,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/imperial-probe-droid-1365.php</v>
       </c>
       <c r="L744" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-probe-droid-1365.jpg</v>
       </c>
       <c r="M744" t="str">
         <v/>
@@ -37684,7 +37684,7 @@
         <v>https://www.actionfigure411.com/star-wars/6-black-series/deluxe-sets/luke-skywalker-dagobah-yoda-1433.php</v>
       </c>
       <c r="L745" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-dagobah-yoda-1433.jpg</v>
       </c>
       <c r="M745" t="str">
         <v/>
@@ -37734,7 +37734,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/ahsoka-tano-lightsaber-1569.php</v>
       </c>
       <c r="L746" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ahsoka-tano-lightsaber-1569.jpg</v>
       </c>
       <c r="M746" t="str">
         <v/>
@@ -37784,7 +37784,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/darth-revan-lightsaber-1377.php</v>
       </c>
       <c r="L747" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-revan-lightsaber-1377.jpg</v>
       </c>
       <c r="M747" t="str">
         <v/>
@@ -37834,7 +37834,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/emperor-palpatine-lightsaber-1512.php</v>
       </c>
       <c r="L748" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/emperor-palpatine-lightsaber-1512.jpg</v>
       </c>
       <c r="M748" t="str">
         <v/>
@@ -37884,7 +37884,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/kylo-ren-elite-lightsaber-1316.php</v>
       </c>
       <c r="L749" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kylo-ren-elite-lightsaber-1316.jpg</v>
       </c>
       <c r="M749" t="str">
         <v/>
@@ -37934,7 +37934,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/mandalorian-darksaber-1616.php</v>
       </c>
       <c r="L750" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mandalorian-darksaber-1616.jpg</v>
       </c>
       <c r="M750" t="str">
         <v/>
@@ -37984,7 +37984,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/rey-skywalker-lightsaber-yellow-force-fx-elite-3218.php</v>
       </c>
       <c r="L751" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rey-skywalker-lightsaber-yellow-force-fx-elite-3218.jpg</v>
       </c>
       <c r="M751" t="str">
         <v/>
@@ -38034,7 +38034,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/darth-vader-force-fx-elite-lightsaber-4601.php</v>
       </c>
       <c r="L752" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-force-fx-elite-lightsaber-4601.jpg</v>
       </c>
       <c r="M752" t="str">
         <v/>
@@ -38084,7 +38084,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/leia-organa-lightsaber-3531.php</v>
       </c>
       <c r="L753" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/leia-organa-lightsaber-3531.jpg</v>
       </c>
       <c r="M753" t="str">
         <v/>
@@ -38134,7 +38134,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/luke-skywalker-elite-lightsaber-green-5430.php</v>
       </c>
       <c r="L754" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-elite-lightsaber-green-5430.jpg</v>
       </c>
       <c r="M754" t="str">
         <v/>
@@ -38184,7 +38184,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/obi-wan-kenobi-force-fx-lightsaber-4178.php</v>
       </c>
       <c r="L755" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-force-fx-lightsaber-4178.jpg</v>
       </c>
       <c r="M755" t="str">
         <v/>
@@ -38234,7 +38234,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/yoda-force-fx-elite-electronic-lightsaber-6444.php</v>
       </c>
       <c r="L756" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/yoda-force-fx-elite-electronic-lightsaber-6444.jpg</v>
       </c>
       <c r="M756" t="str">
         <v/>
@@ -38284,7 +38284,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/ahsoka-tano-lightsaber-7515.php</v>
       </c>
       <c r="L757" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ahsoka-tano-lightsaber-7515.jpg</v>
       </c>
       <c r="M757" t="str">
         <v/>
@@ -38334,7 +38334,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/sabine-wren-lightsaber-7514.php</v>
       </c>
       <c r="L758" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sabine-wren-lightsaber-7514.jpg</v>
       </c>
       <c r="M758" t="str">
         <v/>
@@ -38384,7 +38384,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/baylan-skoll-force-fx-elite-electronic-lightsaber-9049.php</v>
       </c>
       <c r="L759" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/baylan-skoll-force-fx-elite-electronic-lightsaber-9049.jpg</v>
       </c>
       <c r="M759" t="str">
         <v/>
@@ -38434,7 +38434,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/ezra-bridger-lightsaber-10759.php</v>
       </c>
       <c r="L760" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/ezra-bridger-lightsaber-10759.jpg</v>
       </c>
       <c r="M760" t="str">
         <v/>
@@ -38484,7 +38484,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/yoda-lightsaber-110.php</v>
       </c>
       <c r="L761" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/yoda-lightsaber-110.jpg</v>
       </c>
       <c r="M761" t="str">
         <v/>
@@ -38534,7 +38534,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/darth-vader-lightsaber-111.php</v>
       </c>
       <c r="L762" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-lightsaber-111.jpg</v>
       </c>
       <c r="M762" t="str">
         <v/>
@@ -38584,7 +38584,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/luke-skywalker-lightsaber-blue-112.php</v>
       </c>
       <c r="L763" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-lightsaber-blue-112.jpg</v>
       </c>
       <c r="M763" t="str">
         <v/>
@@ -38634,7 +38634,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/kylo-ren-lightsaber-113.php</v>
       </c>
       <c r="L764" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kylo-ren-lightsaber-113.jpg</v>
       </c>
       <c r="M764" t="str">
         <v/>
@@ -38684,7 +38684,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/luke-skywalker-lightsaber-green-145.php</v>
       </c>
       <c r="L765" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-lightsaber-green-145.jpg</v>
       </c>
       <c r="M765" t="str">
         <v/>
@@ -38734,7 +38734,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/obi-wan-kenobi-lightsaber-anh-266.php</v>
       </c>
       <c r="L766" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-lightsaber-anh-266.jpg</v>
       </c>
       <c r="M766" t="str">
         <v/>
@@ -38784,7 +38784,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/rey-lightsaber-blue-795.php</v>
       </c>
       <c r="L767" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/rey-lightsaber-blue-795.jpg</v>
       </c>
       <c r="M767" t="str">
         <v/>
@@ -38834,7 +38834,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/riot-control-baton-fx-z6-1099.php</v>
       </c>
       <c r="L768" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/riot-control-baton-fx-z6-1099.jpg</v>
       </c>
       <c r="M768" t="str">
         <v/>
@@ -38884,7 +38884,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/mace-windu-lightsaber-1222.php</v>
       </c>
       <c r="L769" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/mace-windu-lightsaber-1222.jpg</v>
       </c>
       <c r="M769" t="str">
         <v/>
@@ -38934,7 +38934,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/obi-wan-kenobi-lightsaber-tpm-1564.php</v>
       </c>
       <c r="L770" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/obi-wan-kenobi-lightsaber-tpm-1564.jpg</v>
       </c>
       <c r="M770" t="str">
         <v/>
@@ -38984,7 +38984,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/darth-maul-lightsaber-1223.php</v>
       </c>
       <c r="L771" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-maul-lightsaber-1223.jpg</v>
       </c>
       <c r="M771" t="str">
         <v/>
@@ -39034,7 +39034,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/asajj-ventress-lightsaber-1565.php</v>
       </c>
       <c r="L772" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/asajj-ventress-lightsaber-1565.jpg</v>
       </c>
       <c r="M772" t="str">
         <v/>
@@ -39084,7 +39084,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/kit-fisto-lightsaber-1567.php</v>
       </c>
       <c r="L773" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kit-fisto-lightsaber-1567.jpg</v>
       </c>
       <c r="M773" t="str">
         <v/>
@@ -39134,7 +39134,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/lightsabers/count-dooku-lightsaber-1568.php</v>
       </c>
       <c r="L774" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/count-dooku-lightsaber-1568.jpg</v>
       </c>
       <c r="M774" t="str">
         <v/>
@@ -39184,7 +39184,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/kylo-ren-voice-changer-helmet-114.php</v>
       </c>
       <c r="L775" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/kylo-ren-voice-changer-helmet-114.jpg</v>
       </c>
       <c r="M775" t="str">
         <v/>
@@ -39234,7 +39234,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/shadow-trooper-helmet-158.php</v>
       </c>
       <c r="L776" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/shadow-trooper-helmet-158.jpg</v>
       </c>
       <c r="M776" t="str">
         <v/>
@@ -39284,7 +39284,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/stormtrooper-voice-changer-helmet-151.php</v>
       </c>
       <c r="L777" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/stormtrooper-voice-changer-helmet-151.jpg</v>
       </c>
       <c r="M777" t="str">
         <v/>
@@ -39334,7 +39334,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/poe-dameron-helmet-267.php</v>
       </c>
       <c r="L778" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/poe-dameron-helmet-267.jpg</v>
       </c>
       <c r="M778" t="str">
         <v/>
@@ -39384,7 +39384,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/darth-vader-helmet-1041.php</v>
       </c>
       <c r="L779" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-helmet-1041.jpg</v>
       </c>
       <c r="M779" t="str">
         <v/>
@@ -39434,7 +39434,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/shock-trooper-helmet-1087.php</v>
       </c>
       <c r="L780" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/shock-trooper-helmet-1087.jpg</v>
       </c>
       <c r="M780" t="str">
         <v/>
@@ -39484,7 +39484,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/boba-fett-helmet-1299.php</v>
       </c>
       <c r="L781" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-helmet-1299.jpg</v>
       </c>
       <c r="M781" t="str">
         <v/>
@@ -39534,7 +39534,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/incinerator-helmet-1358.php</v>
       </c>
       <c r="L782" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/incinerator-helmet-1358.jpg</v>
       </c>
       <c r="M782" t="str">
         <v/>
@@ -39584,7 +39584,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/luke-skywalker-electronic-x-wing-pilot-helmet-1300.php</v>
       </c>
       <c r="L783" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/luke-skywalker-electronic-x-wing-pilot-helmet-1300.jpg</v>
       </c>
       <c r="M783" t="str">
         <v/>
@@ -39634,7 +39634,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/captain-cardinal-helmet-1622.php</v>
       </c>
       <c r="L784" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/captain-cardinal-helmet-1622.jpg</v>
       </c>
       <c r="M784" t="str">
         <v/>
@@ -39684,7 +39684,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/prototype-boba-fett-helmet-1434.php</v>
       </c>
       <c r="L785" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/prototype-boba-fett-helmet-1434.jpg</v>
       </c>
       <c r="M785" t="str">
         <v/>
@@ -39734,7 +39734,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/boba-fett-re-armored-helmet-1617.php</v>
       </c>
       <c r="L786" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/boba-fett-re-armored-helmet-1617.jpg</v>
       </c>
       <c r="M786" t="str">
         <v/>
@@ -39784,7 +39784,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/death-watch-mandalorian-helmet-2386.php</v>
       </c>
       <c r="L787" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/death-watch-mandalorian-helmet-2386.jpg</v>
       </c>
       <c r="M787" t="str">
         <v/>
@@ -39834,7 +39834,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/first-order-stormtrooper-helmet-1871.php</v>
       </c>
       <c r="L788" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/first-order-stormtrooper-helmet-1871.jpg</v>
       </c>
       <c r="M788" t="str">
         <v/>
@@ -39884,7 +39884,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/the-mandalorian-helmet-1586.php</v>
       </c>
       <c r="L789" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-mandalorian-helmet-1586.jpg</v>
       </c>
       <c r="M789" t="str">
         <v/>
@@ -39934,7 +39934,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/wedge-antilles-helmet-2081.php</v>
       </c>
       <c r="L790" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/wedge-antilles-helmet-2081.jpg</v>
       </c>
       <c r="M790" t="str">
         <v/>
@@ -39984,7 +39984,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/bo-katan-kryze-helmet-3736.php</v>
       </c>
       <c r="L791" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/bo-katan-kryze-helmet-3736.jpg</v>
       </c>
       <c r="M791" t="str">
         <v/>
@@ -40034,7 +40034,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/trapper-wolf-helmet-4131.php</v>
       </c>
       <c r="L792" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/trapper-wolf-helmet-4131.jpg</v>
       </c>
       <c r="M792" t="str">
         <v/>
@@ -40084,7 +40084,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/332nd-ahsokas-clone-trooper-helmet-6393.php</v>
       </c>
       <c r="L793" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/332nd-ahsokas-clone-trooper-helmet-6393.jpg</v>
       </c>
       <c r="M793" t="str">
         <v/>
@@ -40134,7 +40134,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/artillery-stormtrooper-helmet-4282.php</v>
       </c>
       <c r="L794" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/artillery-stormtrooper-helmet-4282.jpg</v>
       </c>
       <c r="M794" t="str">
         <v/>
@@ -40184,7 +40184,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/axe-woves-premium-electronic-helmet-6652.php</v>
       </c>
       <c r="L795" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/axe-woves-premium-electronic-helmet-6652.jpg</v>
       </c>
       <c r="M795" t="str">
         <v/>
@@ -40234,7 +40234,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/darth-vader-premium-helmet-4179.php</v>
       </c>
       <c r="L796" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/darth-vader-premium-helmet-4179.jpg</v>
       </c>
       <c r="M796" t="str">
         <v/>
@@ -40284,7 +40284,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/phase-ii-clone-trooper-premium-electronic-5371.php</v>
       </c>
       <c r="L797" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/phase-ii-clone-trooper-premium-electronic-5371.jpg</v>
       </c>
       <c r="M797" t="str">
         <v/>
@@ -40334,7 +40334,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/sabine-wren-helmet-7212.php</v>
       </c>
       <c r="L798" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/sabine-wren-helmet-7212.jpg</v>
       </c>
       <c r="M798" t="str">
         <v/>
@@ -40384,7 +40384,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/scout-trooper-helmet-6883.php</v>
       </c>
       <c r="L799" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/scout-trooper-helmet-6883.jpg</v>
       </c>
       <c r="M799" t="str">
         <v/>
@@ -40434,7 +40434,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/carson-teva-helmet-7476.php</v>
       </c>
       <c r="L800" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/carson-teva-helmet-7476.jpg</v>
       </c>
       <c r="M800" t="str">
         <v/>
@@ -40484,7 +40484,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/clone-captain-rex-helmet-7513.php</v>
       </c>
       <c r="L801" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-captain-rex-helmet-7513.jpg</v>
       </c>
       <c r="M801" t="str">
         <v/>
@@ -40534,7 +40534,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/moff-gideon-premium-electronic-helmet-8347.php</v>
       </c>
       <c r="L802" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/moff-gideon-premium-electronic-helmet-8347.jpg</v>
       </c>
       <c r="M802" t="str">
         <v/>
@@ -40584,7 +40584,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/the-stranger-helmet-8699.php</v>
       </c>
       <c r="L803" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-stranger-helmet-8699.jpg</v>
       </c>
       <c r="M803" t="str">
         <v/>
@@ -40634,7 +40634,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/clone-commander-cody-helmet-10767.php</v>
       </c>
       <c r="L804" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-commander-cody-helmet-10767.jpg</v>
       </c>
       <c r="M804" t="str">
         <v/>
@@ -40684,7 +40684,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/clone-trooper-501st-legion-helmet-11048.php</v>
       </c>
       <c r="L805" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/clone-trooper-501st-legion-helmet-11048.jpg</v>
       </c>
       <c r="M805" t="str">
         <v/>
@@ -40734,7 +40734,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/imperial-death-trooper-helmet-rogue-one-10692.php</v>
       </c>
       <c r="L806" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/imperial-death-trooper-helmet-rogue-one-10692.jpg</v>
       </c>
       <c r="M806" t="str">
         <v/>
@@ -40784,7 +40784,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/shoretrooper-andor-premium-electronic-helmet-11873.php</v>
       </c>
       <c r="L807" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/shoretrooper-andor-premium-electronic-helmet-11873.jpg</v>
       </c>
       <c r="M807" t="str">
         <v/>
@@ -40834,7 +40834,7 @@
         <v>https://www.actionfigure411.com/star-wars/roleplay/helmets/the-armorer-helmet-8867.php</v>
       </c>
       <c r="L808" t="str">
-        <v/>
+        <v>https://www.actionfigure411.com/star-wars/images/the-armorer-helmet-8867.jpg</v>
       </c>
       <c r="M808" t="str">
         <v/>
